--- a/mekanik-elektrik/TMO_MARDIN_MEKANIK_EKIPMAN_ELEKTRIK_GUCLERI.xlsx
+++ b/mekanik-elektrik/TMO_MARDIN_MEKANIK_EKIPMAN_ELEKTRIK_GUCLERI.xlsx
@@ -16,7 +16,7 @@
     <sheet name="VRF Dış Üniteler" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Elektrik Güç Tablosu'!$A$4:$U$39</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Elektrik Güç Tablosu'!$A$4:$U$42</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="405">
   <si>
     <t xml:space="preserve">MEKANİK EKİPMAN ELEKTRİK GÜÇ TABLOSU</t>
   </si>
@@ -418,19 +418,61 @@
     <t xml:space="preserve">Edirne VRF notu</t>
   </si>
   <si>
-    <t xml:space="preserve">SPLT-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Server Odası Split Klima (İç+Dış)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.000 Btu/h (3,5 kW), 7/24, 1 asıl + 1 yedek</t>
+    <t xml:space="preserve">MSP-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi Split Dış Ünite (ASIL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 iç üniteli, 6,8 kW soğutma, inverter, -15 °C kış soğutma kiti, 7/24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIŞ CEPHE (Z-10 ÖNÜ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teknik hacim yük hesabı (Soğutma Yükü sayfası)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSP-1Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi Split Dış Ünite (YEDEK)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asıl ile aynı; arızada otomatik devreye giriş + haftalık rotasyon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yedeklilik: 1 asıl + 1 yedek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS-1/1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi Split Duvar Tipi İç Ünite - Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,5 kW soğutma (12.000 Btu/h), 7/24</t>
   </si>
   <si>
     <t xml:space="preserve">SERVER ODASI</t>
   </si>
   <si>
-    <t xml:space="preserve">Edirne SPLT-1 eşdeğeri</t>
+    <t xml:space="preserve">Teknik hacim yük hesabı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS-1/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi Split Duvar Tipi İç Ünite - Elk. Pano O.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,5 kW soğutma (9.000 Btu/h), 7/24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELK.ANA PANO O.</t>
   </si>
   <si>
     <t xml:space="preserve">VRF-1A</t>
@@ -562,6 +604,9 @@
     <t xml:space="preserve">Zemin Kat Tali Panosu</t>
   </si>
   <si>
+    <t xml:space="preserve">Ana Dağıtım Panosu - Z-10 Server / Z-11 Pano odası multi split (7/24)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1. Kat Tali Panosu</t>
   </si>
   <si>
@@ -1075,6 +1120,51 @@
     <t xml:space="preserve">Mavi hücreler girdi olup değiştirildiğinde tüm yükler ve "VRF İç Üniteler" sayfasındaki kapasite kontrolü yeniden hesaplanır.</t>
   </si>
   <si>
+    <t xml:space="preserve">TEKNİK HACİMLER - MULTİ SPLİT SOĞUTMA YÜKÜ (Z-10 Server + Z-11 Elektrik Ana Pano Odası; 1 asıl + 1 yedek dış ünite)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ünite Kodu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İç Isı Yükü (W)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aydınlatma (W)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarf + İnfiltrasyon (W/m²)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarf + İnfiltrasyon (W)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOPLAM YÜK (kW) (emniyetli)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İç Ünite Kap. (kW)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kontrol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z-10 SERVER ODASI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Server/network kabini ısı yükü (1 kabin, ön değer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z-11 ELK.ANA PANO O.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana dağıtım panosu + kompanzasyon + UPS kayıpları (ön değer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTİ SPLİT DIŞ ÜNİTE (her biri: asıl / yedek)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varsayım: iç ısı yükleri ön değerdir (server kabin ve pano kayıpları satın alınacak ekipmana göre güncellenmelidir). Zarf + infiltrasyon 30 W/m² alınmıştır. Dış ünite, iki iç ünite kapasite toplamının en az %90'ını karşılamalıdır. 7/24 çalışma için kış soğutma (low ambient) kiti gereklidir.</t>
+  </si>
+  <si>
     <t xml:space="preserve">VRF İÇ ÜNİTE SEÇİM TABLOSU (KASET TİP 4 YÖNE ÜFLEMELİ)</t>
   </si>
   <si>
@@ -1094,9 +1184,6 @@
   </si>
   <si>
     <t xml:space="preserve">Toplam Soğ. Kap. (kW)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kontrol</t>
   </si>
   <si>
     <t xml:space="preserve">Toplam Isıt. Kap. (kW)</t>
@@ -1194,7 +1281,7 @@
     <numFmt numFmtId="170" formatCode="0.000"/>
     <numFmt numFmtId="171" formatCode="0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1278,6 +1365,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1360,7 +1455,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1470,6 +1565,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1790,7 +1889,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:U55"/>
+  <dimension ref="A1:U58"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3327,7 +3426,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="n">
         <v>21</v>
       </c>
@@ -3350,21 +3449,21 @@
         <v>28</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="K25" s="8" t="n">
         <f aca="false">H25*J25</f>
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="L25" s="8" t="n">
         <f aca="false">I25*J25</f>
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="M25" s="6" t="n">
         <v>230</v>
@@ -3377,24 +3476,24 @@
       </c>
       <c r="P25" s="8" t="n">
         <f aca="false">IF(OR(J25=0,M25=0),0,IF(N25=3,J25*1000/(SQRT(3)*M25*O25),J25*1000/(M25*O25)))</f>
-        <v>5.31400966183575</v>
+        <v>10.1449275362319</v>
       </c>
       <c r="Q25" s="4" t="n">
         <f aca="false">IF(P25=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P25*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R25" s="4" t="str">
         <f aca="false">IF(P25=0,"-",IF(N25=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P25*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
         <v>3x2,5 mm²</v>
       </c>
       <c r="S25" s="5" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="T25" s="5" t="s">
         <v>30</v>
       </c>
       <c r="U25" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3402,10 +3501,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>129</v>
@@ -3414,7 +3513,7 @@
         <v>130</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>28</v>
@@ -3423,69 +3522,68 @@
         <v>1</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="9" t="n">
-        <f aca="false">'VRF Dış Üniteler'!E5</f>
-        <v>13.8</v>
+        <v>0</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>2.1</v>
       </c>
       <c r="K26" s="8" t="n">
         <f aca="false">H26*J26</f>
-        <v>13.8</v>
+        <v>2.1</v>
       </c>
       <c r="L26" s="8" t="n">
         <f aca="false">I26*J26</f>
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>400</v>
+        <v>230</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O26" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="P26" s="8" t="n">
         <f aca="false">IF(OR(J26=0,M26=0),0,IF(N26=3,J26*1000/(SQRT(3)*M26*O26),J26*1000/(M26*O26)))</f>
-        <v>20.9669308284654</v>
+        <v>10.1449275362319</v>
       </c>
       <c r="Q26" s="4" t="n">
         <f aca="false">IF(P26=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P26*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="R26" s="4" t="str">
         <f aca="false">IF(P26=0,"-",IF(N26=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P26*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
-        <v>5x6 mm²</v>
+        <v>3x2,5 mm²</v>
       </c>
       <c r="S26" s="5" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="T26" s="5" t="s">
         <v>30</v>
       </c>
       <c r="U26" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
       <c r="B27" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>130</v>
-      </c>
       <c r="F27" s="5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>28</v>
@@ -3496,67 +3594,66 @@
       <c r="I27" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="9" t="n">
-        <f aca="false">'VRF Dış Üniteler'!E6</f>
-        <v>13.8</v>
+      <c r="J27" s="7" t="n">
+        <v>0.04</v>
       </c>
       <c r="K27" s="8" t="n">
         <f aca="false">H27*J27</f>
-        <v>13.8</v>
+        <v>0.04</v>
       </c>
       <c r="L27" s="8" t="n">
         <f aca="false">I27*J27</f>
-        <v>13.8</v>
+        <v>0.04</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>400</v>
+        <v>230</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="P27" s="8" t="n">
         <f aca="false">IF(OR(J27=0,M27=0),0,IF(N27=3,J27*1000/(SQRT(3)*M27*O27),J27*1000/(M27*O27)))</f>
-        <v>20.9669308284654</v>
+        <v>0.193236714975845</v>
       </c>
       <c r="Q27" s="4" t="n">
         <f aca="false">IF(P27=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P27*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="R27" s="4" t="str">
         <f aca="false">IF(P27=0,"-",IF(N27=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P27*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
-        <v>5x6 mm²</v>
+        <v>3x2,5 mm²</v>
       </c>
       <c r="S27" s="5" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="T27" s="5" t="s">
         <v>30</v>
       </c>
       <c r="U27" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="n">
         <v>24</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>28</v>
@@ -3567,47 +3664,46 @@
       <c r="I28" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="9" t="n">
-        <f aca="false">'VRF Dış Üniteler'!E7</f>
-        <v>21</v>
+      <c r="J28" s="7" t="n">
+        <v>0.04</v>
       </c>
       <c r="K28" s="8" t="n">
         <f aca="false">H28*J28</f>
-        <v>21</v>
+        <v>0.04</v>
       </c>
       <c r="L28" s="8" t="n">
         <f aca="false">I28*J28</f>
-        <v>21</v>
+        <v>0.04</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>400</v>
+        <v>230</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="P28" s="8" t="n">
         <f aca="false">IF(OR(J28=0,M28=0),0,IF(N28=3,J28*1000/(SQRT(3)*M28*O28),J28*1000/(M28*O28)))</f>
-        <v>31.9061990867951</v>
+        <v>0.193236714975845</v>
       </c>
       <c r="Q28" s="4" t="n">
         <f aca="false">IF(P28=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P28*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="R28" s="4" t="str">
         <f aca="false">IF(P28=0,"-",IF(N28=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P28*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
-        <v>5x10 mm²</v>
+        <v>3x2,5 mm²</v>
       </c>
       <c r="S28" s="5" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="T28" s="5" t="s">
         <v>30</v>
       </c>
       <c r="U28" s="5" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3615,72 +3711,70 @@
         <v>25</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H29" s="10" t="n">
-        <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G29,'VRF İç Üniteler'!$G$5:$G$34,B29,'VRF İç Üniteler'!$O$5:$O$34,"VRF-1")</f>
-        <v>3</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <f aca="false">H29</f>
-        <v>3</v>
+      <c r="H29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="J29" s="9" t="n">
-        <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B29,Tablolar!$A$5:$A$10,0))/1000</f>
-        <v>0.05</v>
+        <f aca="false">'VRF Dış Üniteler'!E5</f>
+        <v>13.8</v>
       </c>
       <c r="K29" s="8" t="n">
         <f aca="false">H29*J29</f>
-        <v>0.15</v>
+        <v>13.8</v>
       </c>
       <c r="L29" s="8" t="n">
         <f aca="false">I29*J29</f>
-        <v>0.15</v>
+        <v>13.8</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>230</v>
+        <v>400</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="P29" s="8" t="n">
         <f aca="false">IF(OR(J29=0,M29=0),0,IF(N29=3,J29*1000/(SQRT(3)*M29*O29),J29*1000/(M29*O29)))</f>
-        <v>0.241545893719807</v>
+        <v>20.9669308284654</v>
       </c>
       <c r="Q29" s="4" t="n">
         <f aca="false">IF(P29=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P29*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="R29" s="4" t="str">
         <f aca="false">IF(P29=0,"-",IF(N29=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P29*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
-        <v>3x2,5 mm²</v>
+        <v>5x6 mm²</v>
       </c>
       <c r="S29" s="5" t="s">
-        <v>88</v>
+        <v>146</v>
       </c>
       <c r="T29" s="5" t="s">
         <v>30</v>
       </c>
       <c r="U29" s="5" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3688,72 +3782,70 @@
         <v>26</v>
       </c>
       <c r="B30" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>139</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>144</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H30" s="10" t="n">
-        <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G30,'VRF İç Üniteler'!$G$5:$G$34,B30,'VRF İç Üniteler'!$O$5:$O$34,"VRF-1")</f>
-        <v>2</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <f aca="false">H30</f>
-        <v>2</v>
+      <c r="H30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="J30" s="9" t="n">
-        <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B30,Tablolar!$A$5:$A$10,0))/1000</f>
-        <v>0.062</v>
+        <f aca="false">'VRF Dış Üniteler'!E6</f>
+        <v>13.8</v>
       </c>
       <c r="K30" s="8" t="n">
         <f aca="false">H30*J30</f>
-        <v>0.124</v>
+        <v>13.8</v>
       </c>
       <c r="L30" s="8" t="n">
         <f aca="false">I30*J30</f>
-        <v>0.124</v>
+        <v>13.8</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>230</v>
+        <v>400</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="P30" s="8" t="n">
         <f aca="false">IF(OR(J30=0,M30=0),0,IF(N30=3,J30*1000/(SQRT(3)*M30*O30),J30*1000/(M30*O30)))</f>
-        <v>0.29951690821256</v>
+        <v>20.9669308284654</v>
       </c>
       <c r="Q30" s="4" t="n">
         <f aca="false">IF(P30=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P30*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="R30" s="4" t="str">
         <f aca="false">IF(P30=0,"-",IF(N30=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P30*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
-        <v>3x2,5 mm²</v>
+        <v>5x6 mm²</v>
       </c>
       <c r="S30" s="5" t="s">
-        <v>88</v>
+        <v>146</v>
       </c>
       <c r="T30" s="5" t="s">
         <v>30</v>
       </c>
       <c r="U30" s="5" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3761,72 +3853,70 @@
         <v>27</v>
       </c>
       <c r="B31" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>145</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>141</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H31" s="10" t="n">
-        <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G31,'VRF İç Üniteler'!$G$5:$G$34,B31,'VRF İç Üniteler'!$O$5:$O$34,"VRF-1")</f>
-        <v>2</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <f aca="false">H31</f>
-        <v>2</v>
+      <c r="H31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="J31" s="9" t="n">
-        <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B31,Tablolar!$A$5:$A$10,0))/1000</f>
-        <v>0.05</v>
+        <f aca="false">'VRF Dış Üniteler'!E7</f>
+        <v>21</v>
       </c>
       <c r="K31" s="8" t="n">
         <f aca="false">H31*J31</f>
-        <v>0.1</v>
+        <v>21</v>
       </c>
       <c r="L31" s="8" t="n">
         <f aca="false">I31*J31</f>
-        <v>0.1</v>
+        <v>21</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>230</v>
+        <v>400</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="P31" s="8" t="n">
         <f aca="false">IF(OR(J31=0,M31=0),0,IF(N31=3,J31*1000/(SQRT(3)*M31*O31),J31*1000/(M31*O31)))</f>
-        <v>0.241545893719807</v>
+        <v>31.9061990867951</v>
       </c>
       <c r="Q31" s="4" t="n">
         <f aca="false">IF(P31=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P31*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="R31" s="4" t="str">
         <f aca="false">IF(P31=0,"-",IF(N31=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P31*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
-        <v>3x2,5 mm²</v>
+        <v>5x10 mm²</v>
       </c>
       <c r="S31" s="5" t="s">
-        <v>88</v>
+        <v>146</v>
       </c>
       <c r="T31" s="5" t="s">
         <v>30</v>
       </c>
       <c r="U31" s="5" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3834,42 +3924,42 @@
         <v>28</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H32" s="10" t="n">
         <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G32,'VRF İç Üniteler'!$G$5:$G$34,B32,'VRF İç Üniteler'!$O$5:$O$34,"VRF-1")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I32" s="4" t="n">
         <f aca="false">H32</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J32" s="9" t="n">
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B32,Tablolar!$A$5:$A$10,0))/1000</f>
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="K32" s="8" t="n">
         <f aca="false">H32*J32</f>
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="L32" s="8" t="n">
         <f aca="false">I32*J32</f>
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="M32" s="6" t="n">
         <v>230</v>
@@ -3882,7 +3972,7 @@
       </c>
       <c r="P32" s="8" t="n">
         <f aca="false">IF(OR(J32=0,M32=0),0,IF(N32=3,J32*1000/(SQRT(3)*M32*O32),J32*1000/(M32*O32)))</f>
-        <v>0.289855072463768</v>
+        <v>0.241545893719807</v>
       </c>
       <c r="Q32" s="4" t="n">
         <f aca="false">IF(P32=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P32*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
@@ -3899,7 +3989,7 @@
         <v>30</v>
       </c>
       <c r="U32" s="5" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3907,42 +3997,42 @@
         <v>29</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="H33" s="10" t="n">
         <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G33,'VRF İç Üniteler'!$G$5:$G$34,B33,'VRF İç Üniteler'!$O$5:$O$34,"VRF-1")</f>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I33" s="4" t="n">
         <f aca="false">H33</f>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J33" s="9" t="n">
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B33,Tablolar!$A$5:$A$10,0))/1000</f>
-        <v>0.05</v>
+        <v>0.062</v>
       </c>
       <c r="K33" s="8" t="n">
         <f aca="false">H33*J33</f>
-        <v>0.35</v>
+        <v>0.124</v>
       </c>
       <c r="L33" s="8" t="n">
         <f aca="false">I33*J33</f>
-        <v>0.35</v>
+        <v>0.124</v>
       </c>
       <c r="M33" s="6" t="n">
         <v>230</v>
@@ -3955,7 +4045,7 @@
       </c>
       <c r="P33" s="8" t="n">
         <f aca="false">IF(OR(J33=0,M33=0),0,IF(N33=3,J33*1000/(SQRT(3)*M33*O33),J33*1000/(M33*O33)))</f>
-        <v>0.241545893719807</v>
+        <v>0.29951690821256</v>
       </c>
       <c r="Q33" s="4" t="n">
         <f aca="false">IF(P33=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P33*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
@@ -3966,13 +4056,13 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S33" s="5" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="T33" s="5" t="s">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="U33" s="5" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3980,22 +4070,22 @@
         <v>30</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="H34" s="10" t="n">
         <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G34,'VRF İç Üniteler'!$G$5:$G$34,B34,'VRF İç Üniteler'!$O$5:$O$34,"VRF-1")</f>
@@ -4007,15 +4097,15 @@
       </c>
       <c r="J34" s="9" t="n">
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B34,Tablolar!$A$5:$A$10,0))/1000</f>
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="K34" s="8" t="n">
         <f aca="false">H34*J34</f>
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="L34" s="8" t="n">
         <f aca="false">I34*J34</f>
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="M34" s="6" t="n">
         <v>230</v>
@@ -4028,7 +4118,7 @@
       </c>
       <c r="P34" s="8" t="n">
         <f aca="false">IF(OR(J34=0,M34=0),0,IF(N34=3,J34*1000/(SQRT(3)*M34*O34),J34*1000/(M34*O34)))</f>
-        <v>0.289855072463768</v>
+        <v>0.241545893719807</v>
       </c>
       <c r="Q34" s="4" t="n">
         <f aca="false">IF(P34=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P34*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
@@ -4039,13 +4129,13 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S34" s="5" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="T34" s="5" t="s">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="U34" s="5" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4053,30 +4143,30 @@
         <v>31</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="H35" s="10" t="n">
         <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G35,'VRF İç Üniteler'!$G$5:$G$34,B35,'VRF İç Üniteler'!$O$5:$O$34,"VRF-1")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I35" s="4" t="n">
         <f aca="false">H35</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J35" s="9" t="n">
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B35,Tablolar!$A$5:$A$10,0))/1000</f>
@@ -4084,11 +4174,11 @@
       </c>
       <c r="K35" s="8" t="n">
         <f aca="false">H35*J35</f>
-        <v>0.24</v>
+        <v>0.06</v>
       </c>
       <c r="L35" s="8" t="n">
         <f aca="false">I35*J35</f>
-        <v>0.24</v>
+        <v>0.06</v>
       </c>
       <c r="M35" s="6" t="n">
         <v>230</v>
@@ -4112,13 +4202,13 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S35" s="5" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="T35" s="5" t="s">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="U35" s="5" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4126,30 +4216,30 @@
         <v>32</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>103</v>
       </c>
       <c r="H36" s="10" t="n">
         <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G36,'VRF İç Üniteler'!$G$5:$G$34,B36,'VRF İç Üniteler'!$O$5:$O$34,"VRF-1")</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I36" s="4" t="n">
         <f aca="false">H36</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J36" s="9" t="n">
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B36,Tablolar!$A$5:$A$10,0))/1000</f>
@@ -4157,11 +4247,11 @@
       </c>
       <c r="K36" s="8" t="n">
         <f aca="false">H36*J36</f>
-        <v>0.05</v>
+        <v>0.35</v>
       </c>
       <c r="L36" s="8" t="n">
         <f aca="false">I36*J36</f>
-        <v>0.05</v>
+        <v>0.35</v>
       </c>
       <c r="M36" s="6" t="n">
         <v>230</v>
@@ -4191,7 +4281,7 @@
         <v>105</v>
       </c>
       <c r="U36" s="5" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4199,30 +4289,30 @@
         <v>33</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H37" s="10" t="n">
-        <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G37,'VRF İç Üniteler'!$G$5:$G$34,B37,'VRF İç Üniteler'!$O$5:$O$34,"VRF-2")</f>
-        <v>9</v>
+        <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G37,'VRF İç Üniteler'!$G$5:$G$34,B37,'VRF İç Üniteler'!$O$5:$O$34,"VRF-1")</f>
+        <v>2</v>
       </c>
       <c r="I37" s="4" t="n">
         <f aca="false">H37</f>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J37" s="9" t="n">
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B37,Tablolar!$A$5:$A$10,0))/1000</f>
@@ -4230,11 +4320,11 @@
       </c>
       <c r="K37" s="8" t="n">
         <f aca="false">H37*J37</f>
-        <v>0.54</v>
+        <v>0.12</v>
       </c>
       <c r="L37" s="8" t="n">
         <f aca="false">I37*J37</f>
-        <v>0.54</v>
+        <v>0.12</v>
       </c>
       <c r="M37" s="6" t="n">
         <v>230</v>
@@ -4258,13 +4348,13 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S37" s="5" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="T37" s="5" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="U37" s="5" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4272,25 +4362,25 @@
         <v>34</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H38" s="10" t="n">
-        <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G38,'VRF İç Üniteler'!$G$5:$G$34,B38,'VRF İç Üniteler'!$O$5:$O$34,"VRF-2")</f>
+        <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G38,'VRF İç Üniteler'!$G$5:$G$34,B38,'VRF İç Üniteler'!$O$5:$O$34,"VRF-1")</f>
         <v>4</v>
       </c>
       <c r="I38" s="4" t="n">
@@ -4331,13 +4421,13 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S38" s="5" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="T38" s="5" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="U38" s="5" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4345,30 +4435,30 @@
         <v>35</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H39" s="10" t="n">
-        <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G39,'VRF İç Üniteler'!$G$5:$G$34,B39,'VRF İç Üniteler'!$O$5:$O$34,"VRF-2")</f>
-        <v>2</v>
+        <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G39,'VRF İç Üniteler'!$G$5:$G$34,B39,'VRF İç Üniteler'!$O$5:$O$34,"VRF-1")</f>
+        <v>1</v>
       </c>
       <c r="I39" s="4" t="n">
         <f aca="false">H39</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" s="9" t="n">
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B39,Tablolar!$A$5:$A$10,0))/1000</f>
@@ -4376,11 +4466,11 @@
       </c>
       <c r="K39" s="8" t="n">
         <f aca="false">H39*J39</f>
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="L39" s="8" t="n">
         <f aca="false">I39*J39</f>
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="M39" s="6" t="n">
         <v>230</v>
@@ -4404,165 +4494,282 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S39" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="T39" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="U39" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="H40" s="10" t="n">
+        <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G40,'VRF İç Üniteler'!$G$5:$G$34,B40,'VRF İç Üniteler'!$O$5:$O$34,"VRF-2")</f>
+        <v>9</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <f aca="false">H40</f>
+        <v>9</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B40,Tablolar!$A$5:$A$10,0))/1000</f>
+        <v>0.06</v>
+      </c>
+      <c r="K40" s="8" t="n">
+        <f aca="false">H40*J40</f>
+        <v>0.54</v>
+      </c>
+      <c r="L40" s="8" t="n">
+        <f aca="false">I40*J40</f>
+        <v>0.54</v>
+      </c>
+      <c r="M40" s="6" t="n">
+        <v>230</v>
+      </c>
+      <c r="N40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" s="7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P40" s="8" t="n">
+        <f aca="false">IF(OR(J40=0,M40=0),0,IF(N40=3,J40*1000/(SQRT(3)*M40*O40),J40*1000/(M40*O40)))</f>
+        <v>0.289855072463768</v>
+      </c>
+      <c r="Q40" s="4" t="n">
+        <f aca="false">IF(P40=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P40*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
+        <v>10</v>
+      </c>
+      <c r="R40" s="4" t="str">
+        <f aca="false">IF(P40=0,"-",IF(N40=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P40*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
+        <v>3x2,5 mm²</v>
+      </c>
+      <c r="S40" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="T39" s="5" t="s">
+      <c r="T40" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="U39" s="5" t="s">
+      <c r="U40" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="11"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="11"/>
-      <c r="O41" s="11"/>
-      <c r="P41" s="11"/>
-      <c r="Q41" s="11"/>
-      <c r="R41" s="11"/>
-      <c r="S41" s="11"/>
-      <c r="T41" s="11"/>
-      <c r="U41" s="11"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
+      <c r="D41" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="H41" s="10" t="n">
+        <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G41,'VRF İç Üniteler'!$G$5:$G$34,B41,'VRF İç Üniteler'!$O$5:$O$34,"VRF-2")</f>
+        <v>4</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <f aca="false">H41</f>
+        <v>4</v>
+      </c>
+      <c r="J41" s="9" t="n">
+        <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B41,Tablolar!$A$5:$A$10,0))/1000</f>
+        <v>0.06</v>
+      </c>
+      <c r="K41" s="8" t="n">
+        <f aca="false">H41*J41</f>
+        <v>0.24</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <f aca="false">I41*J41</f>
+        <v>0.24</v>
+      </c>
+      <c r="M41" s="6" t="n">
+        <v>230</v>
+      </c>
+      <c r="N41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" s="7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P41" s="8" t="n">
+        <f aca="false">IF(OR(J41=0,M41=0),0,IF(N41=3,J41*1000/(SQRT(3)*M41*O41),J41*1000/(M41*O41)))</f>
+        <v>0.289855072463768</v>
+      </c>
+      <c r="Q41" s="4" t="n">
+        <f aca="false">IF(P41=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P41*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
+        <v>10</v>
+      </c>
+      <c r="R41" s="4" t="str">
+        <f aca="false">IF(P41=0,"-",IF(N41=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P41*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
+        <v>3x2,5 mm²</v>
+      </c>
+      <c r="S41" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="T41" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="U41" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="C42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4" t="n">
-        <f aca="false">SUMIF($C$5:$C$39,C42,$H$5:$H$39)</f>
-        <v>8</v>
-      </c>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
+        <v>142</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="H42" s="10" t="n">
+        <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G42,'VRF İç Üniteler'!$G$5:$G$34,B42,'VRF İç Üniteler'!$O$5:$O$34,"VRF-2")</f>
+        <v>2</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <f aca="false">H42</f>
+        <v>2</v>
+      </c>
+      <c r="J42" s="9" t="n">
+        <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B42,Tablolar!$A$5:$A$10,0))/1000</f>
+        <v>0.05</v>
+      </c>
       <c r="K42" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$39,C42,$K$5:$K$39)</f>
-        <v>1.37</v>
+        <f aca="false">H42*J42</f>
+        <v>0.1</v>
       </c>
       <c r="L42" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$39,C42,$L$5:$L$39)</f>
-        <v>1.02</v>
-      </c>
-      <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4"/>
-      <c r="P42" s="4"/>
-      <c r="Q42" s="4"/>
-      <c r="R42" s="4"/>
-      <c r="S42" s="4"/>
-      <c r="T42" s="4"/>
-      <c r="U42" s="4"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4" t="n">
-        <f aca="false">SUMIF($C$5:$C$39,C43,$H$5:$H$39)</f>
-        <v>4</v>
-      </c>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$39,C43,$K$5:$K$39)</f>
-        <v>1.55</v>
-      </c>
-      <c r="L43" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$39,C43,$L$5:$L$39)</f>
-        <v>1.55</v>
-      </c>
-      <c r="M43" s="4"/>
-      <c r="N43" s="4"/>
-      <c r="O43" s="4"/>
-      <c r="P43" s="4"/>
-      <c r="Q43" s="4"/>
-      <c r="R43" s="4"/>
-      <c r="S43" s="4"/>
-      <c r="T43" s="4"/>
-      <c r="U43" s="4"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4" t="n">
-        <f aca="false">SUMIF($C$5:$C$39,C44,$H$5:$H$39)</f>
-        <v>3</v>
-      </c>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$39,C44,$K$5:$K$39)</f>
-        <v>2.6</v>
-      </c>
-      <c r="L44" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$39,C44,$L$5:$L$39)</f>
-        <v>1.85</v>
-      </c>
-      <c r="M44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4"/>
-      <c r="P44" s="4"/>
-      <c r="Q44" s="4"/>
-      <c r="R44" s="4"/>
-      <c r="S44" s="4"/>
-      <c r="T44" s="4"/>
-      <c r="U44" s="4"/>
+        <f aca="false">I42*J42</f>
+        <v>0.1</v>
+      </c>
+      <c r="M42" s="6" t="n">
+        <v>230</v>
+      </c>
+      <c r="N42" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" s="7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P42" s="8" t="n">
+        <f aca="false">IF(OR(J42=0,M42=0),0,IF(N42=3,J42*1000/(SQRT(3)*M42*O42),J42*1000/(M42*O42)))</f>
+        <v>0.241545893719807</v>
+      </c>
+      <c r="Q42" s="4" t="n">
+        <f aca="false">IF(P42=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P42*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
+        <v>10</v>
+      </c>
+      <c r="R42" s="4" t="str">
+        <f aca="false">IF(P42=0,"-",IF(N42=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P42*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
+        <v>3x2,5 mm²</v>
+      </c>
+      <c r="S42" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="T42" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="U42" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="11"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="11"/>
+      <c r="P44" s="11"/>
+      <c r="Q44" s="11"/>
+      <c r="R44" s="11"/>
+      <c r="S44" s="11"/>
+      <c r="T44" s="11"/>
+      <c r="U44" s="11"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="5" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4" t="n">
-        <f aca="false">SUMIF($C$5:$C$39,C45,$H$5:$H$39)</f>
+        <f aca="false">SUMIF($C$5:$C$42,C45,$H$5:$H$42)</f>
         <v>8</v>
       </c>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
       <c r="K45" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$39,C45,$K$5:$K$39)</f>
-        <v>1.7</v>
+        <f aca="false">SUMIF($C$5:$C$42,C45,$K$5:$K$42)</f>
+        <v>1.37</v>
       </c>
       <c r="L45" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$39,C45,$L$5:$L$39)</f>
-        <v>1.7</v>
+        <f aca="false">SUMIF($C$5:$C$42,C45,$L$5:$L$42)</f>
+        <v>1.02</v>
       </c>
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
@@ -4578,25 +4785,25 @@
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="5" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4" t="n">
-        <f aca="false">SUMIF($C$5:$C$39,C46,$H$5:$H$39)</f>
-        <v>3</v>
+        <f aca="false">SUMIF($C$5:$C$42,C46,$H$5:$H$42)</f>
+        <v>4</v>
       </c>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
       <c r="K46" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$39,C46,$K$5:$K$39)</f>
-        <v>2.22</v>
+        <f aca="false">SUMIF($C$5:$C$42,C46,$K$5:$K$42)</f>
+        <v>1.55</v>
       </c>
       <c r="L46" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$39,C46,$L$5:$L$39)</f>
-        <v>1.12</v>
+        <f aca="false">SUMIF($C$5:$C$42,C46,$L$5:$L$42)</f>
+        <v>1.55</v>
       </c>
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
@@ -4612,25 +4819,25 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="5" t="s">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4" t="n">
-        <f aca="false">SUMIF($C$5:$C$39,C47,$H$5:$H$39)</f>
-        <v>40</v>
+        <f aca="false">SUMIF($C$5:$C$42,C47,$H$5:$H$42)</f>
+        <v>3</v>
       </c>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
       <c r="K47" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$39,C47,$K$5:$K$39)</f>
-        <v>50.674</v>
+        <f aca="false">SUMIF($C$5:$C$42,C47,$K$5:$K$42)</f>
+        <v>2.6</v>
       </c>
       <c r="L47" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$39,C47,$L$5:$L$39)</f>
-        <v>50.674</v>
+        <f aca="false">SUMIF($C$5:$C$42,C47,$L$5:$L$42)</f>
+        <v>1.85</v>
       </c>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
@@ -4642,72 +4849,174 @@
       <c r="T47" s="4"/>
       <c r="U47" s="4"/>
     </row>
-    <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="13"/>
-      <c r="B48" s="13"/>
-      <c r="C48" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13" t="n">
-        <f aca="false">SUM(H42:H47)</f>
-        <v>66</v>
-      </c>
-      <c r="I48" s="13"/>
-      <c r="J48" s="13"/>
-      <c r="K48" s="15" t="n">
-        <f aca="false">SUM(K42:K47)</f>
-        <v>60.114</v>
-      </c>
-      <c r="L48" s="15" t="n">
-        <f aca="false">SUM(L42:L47)</f>
-        <v>57.914</v>
-      </c>
-      <c r="M48" s="13"/>
-      <c r="N48" s="13"/>
-      <c r="O48" s="13"/>
-      <c r="P48" s="13"/>
-      <c r="Q48" s="13"/>
-      <c r="R48" s="13"/>
-      <c r="S48" s="13"/>
-      <c r="T48" s="13"/>
-      <c r="U48" s="13"/>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4" t="n">
+        <f aca="false">SUMIF($C$5:$C$42,C48,$H$5:$H$42)</f>
+        <v>8</v>
+      </c>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="8" t="n">
+        <f aca="false">SUMIF($C$5:$C$42,C48,$K$5:$K$42)</f>
+        <v>1.7</v>
+      </c>
+      <c r="L48" s="8" t="n">
+        <f aca="false">SUMIF($C$5:$C$42,C48,$L$5:$L$42)</f>
+        <v>1.7</v>
+      </c>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="4"/>
+      <c r="R48" s="4"/>
+      <c r="S48" s="4"/>
+      <c r="T48" s="4"/>
+      <c r="U48" s="4"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4" t="n">
+        <f aca="false">SUMIF($C$5:$C$42,C49,$H$5:$H$42)</f>
+        <v>5</v>
+      </c>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="8" t="n">
+        <f aca="false">SUMIF($C$5:$C$42,C49,$K$5:$K$42)</f>
+        <v>4.3</v>
+      </c>
+      <c r="L49" s="8" t="n">
+        <f aca="false">SUMIF($C$5:$C$42,C49,$L$5:$L$42)</f>
+        <v>2.2</v>
+      </c>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="4"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="4"/>
+      <c r="R49" s="4"/>
+      <c r="S49" s="4"/>
+      <c r="T49" s="4"/>
+      <c r="U49" s="4"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="16" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="16" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="16" t="s">
-        <v>158</v>
-      </c>
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4" t="n">
+        <f aca="false">SUMIF($C$5:$C$42,C50,$H$5:$H$42)</f>
+        <v>40</v>
+      </c>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="8" t="n">
+        <f aca="false">SUMIF($C$5:$C$42,C50,$K$5:$K$42)</f>
+        <v>50.674</v>
+      </c>
+      <c r="L50" s="8" t="n">
+        <f aca="false">SUMIF($C$5:$C$42,C50,$L$5:$L$42)</f>
+        <v>50.674</v>
+      </c>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="4"/>
+      <c r="R50" s="4"/>
+      <c r="S50" s="4"/>
+      <c r="T50" s="4"/>
+      <c r="U50" s="4"/>
+    </row>
+    <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="13"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13" t="n">
+        <f aca="false">SUM(H45:H50)</f>
+        <v>68</v>
+      </c>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
+      <c r="K51" s="15" t="n">
+        <f aca="false">SUM(K45:K50)</f>
+        <v>62.194</v>
+      </c>
+      <c r="L51" s="15" t="n">
+        <f aca="false">SUM(L45:L50)</f>
+        <v>58.994</v>
+      </c>
+      <c r="M51" s="13"/>
+      <c r="N51" s="13"/>
+      <c r="O51" s="13"/>
+      <c r="P51" s="13"/>
+      <c r="Q51" s="13"/>
+      <c r="R51" s="13"/>
+      <c r="S51" s="13"/>
+      <c r="T51" s="13"/>
+      <c r="U51" s="13"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="16" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="16" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="16" t="s">
-        <v>161</v>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="16" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="16" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="16" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:U39"/>
+  <autoFilter ref="A4:U42"/>
   <mergeCells count="2">
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="A2:U2"/>
@@ -4729,7 +5038,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
@@ -4741,7 +5050,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4751,7 +5060,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4764,10 +5073,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>12</v>
@@ -4776,7 +5085,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4784,47 +5093,47 @@
         <v>29</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="C5" s="4" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$39,A5,'Elektrik Güç Tablosu'!$H$5:$H$39)</f>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A5,'Elektrik Güç Tablosu'!$H$5:$H$42)</f>
         <v>16</v>
       </c>
       <c r="D5" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$39,A5,'Elektrik Güç Tablosu'!$K$5:$K$39)</f>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A5,'Elektrik Güç Tablosu'!$K$5:$K$42)</f>
         <v>5.92</v>
       </c>
       <c r="E5" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$39,A5,'Elektrik Güç Tablosu'!$L$5:$L$39)</f>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A5,'Elektrik Güç Tablosu'!$L$5:$L$42)</f>
         <v>4.82</v>
       </c>
       <c r="F5" s="17" t="n">
-        <f aca="false">IF($E$10=0,0,E5/$E$10)</f>
-        <v>0.083226853610526</v>
+        <f aca="false">IF($E$11=0,0,E5/$E$11)</f>
+        <v>0.0817032240566837</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="C6" s="4" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$39,A6,'Elektrik Güç Tablosu'!$H$5:$H$39)</f>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A6,'Elektrik Güç Tablosu'!$H$5:$H$42)</f>
         <v>3</v>
       </c>
       <c r="D6" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$39,A6,'Elektrik Güç Tablosu'!$K$5:$K$39)</f>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A6,'Elektrik Güç Tablosu'!$K$5:$K$42)</f>
         <v>48.6</v>
       </c>
       <c r="E6" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$39,A6,'Elektrik Güç Tablosu'!$L$5:$L$39)</f>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A6,'Elektrik Güç Tablosu'!$L$5:$L$42)</f>
         <v>48.6</v>
       </c>
       <c r="F6" s="17" t="n">
-        <f aca="false">IF($E$10=0,0,E6/$E$10)</f>
-        <v>0.839175328936009</v>
+        <f aca="false">IF($E$11=0,0,E6/$E$11)</f>
+        <v>0.823812591110961</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4832,215 +5141,239 @@
         <v>88</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="C7" s="4" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$39,A7,'Elektrik Güç Tablosu'!$H$5:$H$39)</f>
-        <v>14</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A7,'Elektrik Güç Tablosu'!$H$5:$H$42)</f>
+        <v>12</v>
       </c>
       <c r="D7" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$39,A7,'Elektrik Güç Tablosu'!$K$5:$K$39)</f>
-        <v>3.254</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A7,'Elektrik Güç Tablosu'!$K$5:$K$42)</f>
+        <v>1.054</v>
       </c>
       <c r="E7" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$39,A7,'Elektrik Güç Tablosu'!$L$5:$L$39)</f>
-        <v>2.154</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A7,'Elektrik Güç Tablosu'!$L$5:$L$42)</f>
+        <v>1.054</v>
       </c>
       <c r="F7" s="17" t="n">
-        <f aca="false">IF($E$10=0,0,E7/$E$10)</f>
-        <v>0.0371930793935836</v>
+        <f aca="false">IF($E$11=0,0,E7/$E$11)</f>
+        <v>0.0178662236837645</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="C8" s="4" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$39,A8,'Elektrik Güç Tablosu'!$H$5:$H$39)</f>
-        <v>15</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A8,'Elektrik Güç Tablosu'!$H$5:$H$42)</f>
+        <v>4</v>
       </c>
       <c r="D8" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$39,A8,'Elektrik Güç Tablosu'!$K$5:$K$39)</f>
-        <v>1.01</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A8,'Elektrik Güç Tablosu'!$K$5:$K$42)</f>
+        <v>4.28</v>
       </c>
       <c r="E8" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$39,A8,'Elektrik Güç Tablosu'!$L$5:$L$39)</f>
-        <v>1.01</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A8,'Elektrik Güç Tablosu'!$L$5:$L$42)</f>
+        <v>2.18</v>
       </c>
       <c r="F8" s="17" t="n">
-        <f aca="false">IF($E$10=0,0,E8/$E$10)</f>
-        <v>0.0174396518976413</v>
+        <f aca="false">IF($E$11=0,0,E8/$E$11)</f>
+        <v>0.0369529104654711</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A9,'Elektrik Güç Tablosu'!$H$5:$H$42)</f>
+        <v>15</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A9,'Elektrik Güç Tablosu'!$K$5:$K$42)</f>
+        <v>1.01</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A9,'Elektrik Güç Tablosu'!$L$5:$L$42)</f>
+        <v>1.01</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <f aca="false">IF($E$11=0,0,E9/$E$11)</f>
+        <v>0.0171203851239109</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$39,A9,'Elektrik Güç Tablosu'!$H$5:$H$39)</f>
+      <c r="B10" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A10,'Elektrik Güç Tablosu'!$H$5:$H$42)</f>
         <v>17</v>
       </c>
-      <c r="D9" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$39,A9,'Elektrik Güç Tablosu'!$K$5:$K$39)</f>
+      <c r="D10" s="8" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A10,'Elektrik Güç Tablosu'!$K$5:$K$42)</f>
         <v>1.33</v>
       </c>
-      <c r="E9" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$39,A9,'Elektrik Güç Tablosu'!$L$5:$L$39)</f>
+      <c r="E10" s="8" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A10,'Elektrik Güç Tablosu'!$L$5:$L$42)</f>
         <v>1.33</v>
       </c>
-      <c r="F9" s="17" t="n">
-        <f aca="false">IF($E$10=0,0,E9/$E$10)</f>
-        <v>0.0229650861622406</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13" t="n">
-        <f aca="false">SUM(C5:C9)</f>
-        <v>65</v>
-      </c>
-      <c r="D10" s="15" t="n">
-        <f aca="false">SUM(D5:D9)</f>
-        <v>60.114</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <f aca="false">SUM(E5:E9)</f>
-        <v>57.914</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <f aca="false">SUM(F5:F9)</f>
-        <v>1</v>
+      <c r="F10" s="17" t="n">
+        <f aca="false">IF($E$11=0,0,E10/$E$11)</f>
+        <v>0.0225446655592094</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="D11" s="19" t="n">
-        <f aca="false">D10-'Elektrik Güç Tablosu'!K48</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A11" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13" t="n">
+        <f aca="false">SUM(C5:C10)</f>
+        <v>67</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <f aca="false">SUM(D5:D10)</f>
+        <v>62.194</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <f aca="false">SUM(E5:E10)</f>
+        <v>58.994</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <f aca="false">SUM(F5:F10)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <f aca="false">D11-'Elektrik Güç Tablosu'!K51</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D13" s="3" t="s">
+      <c r="B14" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$39,A14,'Elektrik Güç Tablosu'!$H$5:$H$39)</f>
-        <v>34</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$39,A14,'Elektrik Güç Tablosu'!$K$5:$K$39)</f>
-        <v>57.774</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$39,A14,'Elektrik Güç Tablosu'!$L$5:$L$39)</f>
-        <v>55.574</v>
-      </c>
-      <c r="F14" s="17" t="n">
-        <f aca="false">IF($E$17=0,0,E14/$E$17)</f>
-        <v>0.959595261940118</v>
+      <c r="F14" s="3" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="C15" s="4" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$39,A15,'Elektrik Güç Tablosu'!$H$5:$H$39)</f>
-        <v>15</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$42,A15,'Elektrik Güç Tablosu'!$H$5:$H$42)</f>
+        <v>36</v>
       </c>
       <c r="D15" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$39,A15,'Elektrik Güç Tablosu'!$K$5:$K$39)</f>
-        <v>1.01</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$42,A15,'Elektrik Güç Tablosu'!$K$5:$K$42)</f>
+        <v>59.854</v>
       </c>
       <c r="E15" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$39,A15,'Elektrik Güç Tablosu'!$L$5:$L$39)</f>
-        <v>1.01</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$42,A15,'Elektrik Güç Tablosu'!$L$5:$L$42)</f>
+        <v>56.654</v>
       </c>
       <c r="F15" s="17" t="n">
-        <f aca="false">IF($E$17=0,0,E15/$E$17)</f>
-        <v>0.0174396518976413</v>
+        <f aca="false">IF($E$18=0,0,E15/$E$18)</f>
+        <v>0.96033494931688</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$42,A16,'Elektrik Güç Tablosu'!$H$5:$H$42)</f>
+        <v>15</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$42,A16,'Elektrik Güç Tablosu'!$K$5:$K$42)</f>
+        <v>1.01</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$42,A16,'Elektrik Güç Tablosu'!$L$5:$L$42)</f>
+        <v>1.01</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <f aca="false">IF($E$18=0,0,E16/$E$18)</f>
+        <v>0.0171203851239109</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$39,A16,'Elektrik Güç Tablosu'!$H$5:$H$39)</f>
+      <c r="B17" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$42,A17,'Elektrik Güç Tablosu'!$H$5:$H$42)</f>
         <v>17</v>
       </c>
-      <c r="D16" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$39,A16,'Elektrik Güç Tablosu'!$K$5:$K$39)</f>
+      <c r="D17" s="8" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$42,A17,'Elektrik Güç Tablosu'!$K$5:$K$42)</f>
         <v>1.33</v>
       </c>
-      <c r="E16" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$39,A16,'Elektrik Güç Tablosu'!$L$5:$L$39)</f>
+      <c r="E17" s="8" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$42,A17,'Elektrik Güç Tablosu'!$L$5:$L$42)</f>
         <v>1.33</v>
       </c>
-      <c r="F16" s="17" t="n">
-        <f aca="false">IF($E$17=0,0,E16/$E$17)</f>
-        <v>0.0229650861622406</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13" t="n">
-        <f aca="false">SUM(C14:C16)</f>
-        <v>66</v>
-      </c>
-      <c r="D17" s="15" t="n">
-        <f aca="false">SUM(D14:D16)</f>
-        <v>60.114</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <f aca="false">SUM(E14:E16)</f>
-        <v>57.914</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <f aca="false">SUM(F14:F16)</f>
+      <c r="F17" s="17" t="n">
+        <f aca="false">IF($E$18=0,0,E17/$E$18)</f>
+        <v>0.0225446655592094</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13" t="n">
+        <f aca="false">SUM(C15:C17)</f>
+        <v>68</v>
+      </c>
+      <c r="D18" s="15" t="n">
+        <f aca="false">SUM(D15:D17)</f>
+        <v>62.194</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <f aca="false">SUM(E15:E17)</f>
+        <v>58.994</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <f aca="false">SUM(F15:F17)</f>
         <v>1</v>
       </c>
     </row>
@@ -5080,7 +5413,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5092,7 +5425,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5104,33 +5437,33 @@
     </row>
     <row r="4" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>2.2</v>
@@ -5142,24 +5475,24 @@
         <v>50</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>2.8</v>
@@ -5171,7 +5504,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0</v>
@@ -5180,15 +5513,15 @@
         <v>10</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>3.6</v>
@@ -5200,7 +5533,7 @@
         <v>60</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>10</v>
@@ -5209,15 +5542,15 @@
         <v>16</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>4.5</v>
@@ -5229,7 +5562,7 @@
         <v>60</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>16</v>
@@ -5238,15 +5571,15 @@
         <v>20</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>5.6</v>
@@ -5258,7 +5591,7 @@
         <v>62</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>20</v>
@@ -5267,15 +5600,15 @@
         <v>25</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>7.1</v>
@@ -5287,7 +5620,7 @@
         <v>62</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>25</v>
@@ -5296,7 +5629,7 @@
         <v>32</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5307,7 +5640,7 @@
         <v>40</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5318,7 +5651,7 @@
         <v>50</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5329,7 +5662,7 @@
         <v>63</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5340,12 +5673,12 @@
         <v>80</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H17" s="16" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -5368,7 +5701,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AF55"/>
+  <dimension ref="A1:AF62"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -5394,7 +5727,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5430,7 +5763,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5466,18 +5799,18 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="O4" s="20" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="21"/>
@@ -5485,45 +5818,45 @@
         <v>38.5</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="21"/>
@@ -5531,13 +5864,13 @@
         <v>24</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>37</v>
@@ -5549,7 +5882,7 @@
         <v>10</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="P6" s="6" t="n">
         <v>10</v>
@@ -5567,7 +5900,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="B7" s="21"/>
       <c r="C7" s="21"/>
@@ -5575,13 +5908,13 @@
         <v>1.8</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>217</v>
@@ -5593,7 +5926,7 @@
         <v>17</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="P7" s="6"/>
       <c r="Q7" s="6" t="n">
@@ -5611,7 +5944,7 @@
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="B8" s="21"/>
       <c r="C8" s="21"/>
@@ -5619,13 +5952,13 @@
         <v>0.55</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>307</v>
@@ -5637,7 +5970,7 @@
         <v>15</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="P8" s="6"/>
       <c r="Q8" s="6" t="n">
@@ -5655,7 +5988,7 @@
     </row>
     <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="B9" s="21"/>
       <c r="C9" s="21"/>
@@ -5663,13 +5996,13 @@
         <v>0.7</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>127</v>
@@ -5681,7 +6014,7 @@
         <v>13</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="P9" s="6" t="n">
         <v>2</v>
@@ -5699,7 +6032,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="B10" s="21"/>
       <c r="C10" s="21"/>
@@ -5707,10 +6040,10 @@
         <v>0.5</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="P10" s="6" t="n">
         <v>1.5</v>
@@ -5728,7 +6061,7 @@
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="B11" s="21"/>
       <c r="C11" s="21"/>
@@ -5736,13 +6069,13 @@
         <v>0.4</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="P11" s="6" t="n">
         <v>1.5</v>
@@ -5760,7 +6093,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
@@ -5768,10 +6101,10 @@
         <v>22</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="P12" s="6" t="n">
         <v>4</v>
@@ -5789,7 +6122,7 @@
     </row>
     <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
@@ -5797,10 +6130,10 @@
         <v>4</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="P13" s="6"/>
       <c r="Q13" s="6" t="n">
@@ -5818,7 +6151,7 @@
     </row>
     <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
@@ -5826,10 +6159,10 @@
         <v>3</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="P14" s="6" t="n">
         <v>3</v>
@@ -5847,7 +6180,7 @@
     </row>
     <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
@@ -5856,7 +6189,7 @@
       </c>
       <c r="E15" s="16"/>
       <c r="O15" s="4" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="P15" s="6"/>
       <c r="Q15" s="6" t="n">
@@ -5874,7 +6207,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="21"/>
@@ -5882,12 +6215,12 @@
         <v>10</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
@@ -5901,88 +6234,88 @@
         <v>8</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="W18" s="3" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="X18" s="3" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="Y18" s="3" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="Z18" s="3" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="AA18" s="3" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="AB18" s="3" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="AC18" s="3" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5990,13 +6323,13 @@
         <v>28</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>120</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>8.35</v>
@@ -6032,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="Q19" s="23" t="n">
         <f aca="false">(H19*$K$6+J19*$K$7+L19*$K$8+N19*$K$9)*$D$8*$D$9</f>
@@ -6092,13 +6425,13 @@
         <v>28</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>42.5</v>
@@ -6134,7 +6467,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="5" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="Q20" s="23" t="n">
         <f aca="false">(H20*$K$6+J20*$K$7+L20*$K$8+N20*$K$9)*$D$8*$D$9</f>
@@ -6194,13 +6527,13 @@
         <v>28</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>19.7</v>
@@ -6236,7 +6569,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="5" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="Q21" s="23" t="n">
         <f aca="false">(H21*$K$6+J21*$K$7+L21*$K$8+N21*$K$9)*$D$8*$D$9</f>
@@ -6296,13 +6629,13 @@
         <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>17.66</v>
@@ -6338,7 +6671,7 @@
         <v>0</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="Q22" s="23" t="n">
         <f aca="false">(H22*$K$6+J22*$K$7+L22*$K$8+N22*$K$9)*$D$8*$D$9</f>
@@ -6398,13 +6731,13 @@
         <v>28</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>22.15</v>
@@ -6440,7 +6773,7 @@
         <v>0</v>
       </c>
       <c r="P23" s="5" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="Q23" s="23" t="n">
         <f aca="false">(H23*$K$6+J23*$K$7+L23*$K$8+N23*$K$9)*$D$8*$D$9</f>
@@ -6500,13 +6833,13 @@
         <v>28</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>16.07</v>
@@ -6542,7 +6875,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="5" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="Q24" s="23" t="n">
         <f aca="false">(H24*$K$6+J24*$K$7+L24*$K$8+N24*$K$9)*$D$8*$D$9</f>
@@ -6602,13 +6935,13 @@
         <v>28</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>16.4</v>
@@ -6644,7 +6977,7 @@
         <v>0</v>
       </c>
       <c r="P25" s="5" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="Q25" s="23" t="n">
         <f aca="false">(H25*$K$6+J25*$K$7+L25*$K$8+N25*$K$9)*$D$8*$D$9</f>
@@ -6704,13 +7037,13 @@
         <v>103</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>42.65</v>
@@ -6746,7 +7079,7 @@
         <v>0</v>
       </c>
       <c r="P26" s="5" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="Q26" s="23" t="n">
         <f aca="false">(H26*$K$6+J26*$K$7+L26*$K$8+N26*$K$9)*$D$8*$D$9</f>
@@ -6806,13 +7139,13 @@
         <v>103</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>43.8</v>
@@ -6848,7 +7181,7 @@
         <v>0</v>
       </c>
       <c r="P27" s="5" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="Q27" s="23" t="n">
         <f aca="false">(H27*$K$6+J27*$K$7+L27*$K$8+N27*$K$9)*$D$8*$D$9</f>
@@ -6908,13 +7241,13 @@
         <v>103</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>27.5</v>
@@ -6950,7 +7283,7 @@
         <v>0</v>
       </c>
       <c r="P28" s="5" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="Q28" s="23" t="n">
         <f aca="false">(H28*$K$6+J28*$K$7+L28*$K$8+N28*$K$9)*$D$8*$D$9</f>
@@ -7010,13 +7343,13 @@
         <v>103</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>24.15</v>
@@ -7052,7 +7385,7 @@
         <v>0</v>
       </c>
       <c r="P29" s="5" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="Q29" s="23" t="n">
         <f aca="false">(H29*$K$6+J29*$K$7+L29*$K$8+N29*$K$9)*$D$8*$D$9</f>
@@ -7112,13 +7445,13 @@
         <v>103</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="E30" s="6" t="n">
         <v>21.8</v>
@@ -7154,7 +7487,7 @@
         <v>0</v>
       </c>
       <c r="P30" s="5" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="Q30" s="23" t="n">
         <f aca="false">(H30*$K$6+J30*$K$7+L30*$K$8+N30*$K$9)*$D$8*$D$9</f>
@@ -7214,13 +7547,13 @@
         <v>103</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="E31" s="6" t="n">
         <v>24</v>
@@ -7256,7 +7589,7 @@
         <v>0</v>
       </c>
       <c r="P31" s="5" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="Q31" s="23" t="n">
         <f aca="false">(H31*$K$6+J31*$K$7+L31*$K$8+N31*$K$9)*$D$8*$D$9</f>
@@ -7316,13 +7649,13 @@
         <v>103</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>19.48</v>
@@ -7358,7 +7691,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="5" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="Q32" s="23" t="n">
         <f aca="false">(H32*$K$6+J32*$K$7+L32*$K$8+N32*$K$9)*$D$8*$D$9</f>
@@ -7418,13 +7751,13 @@
         <v>103</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>24.53</v>
@@ -7460,7 +7793,7 @@
         <v>0</v>
       </c>
       <c r="P33" s="5" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="Q33" s="23" t="n">
         <f aca="false">(H33*$K$6+J33*$K$7+L33*$K$8+N33*$K$9)*$D$8*$D$9</f>
@@ -7520,13 +7853,13 @@
         <v>103</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="E34" s="6" t="n">
         <v>39.9</v>
@@ -7562,7 +7895,7 @@
         <v>0</v>
       </c>
       <c r="P34" s="5" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="Q34" s="23" t="n">
         <f aca="false">(H34*$K$6+J34*$K$7+L34*$K$8+N34*$K$9)*$D$8*$D$9</f>
@@ -7622,13 +7955,13 @@
         <v>103</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>39.65</v>
@@ -7664,7 +7997,7 @@
         <v>0</v>
       </c>
       <c r="P35" s="5" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="Q35" s="23" t="n">
         <f aca="false">(H35*$K$6+J35*$K$7+L35*$K$8+N35*$K$9)*$D$8*$D$9</f>
@@ -7724,13 +8057,13 @@
         <v>108</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>24</v>
@@ -7766,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="P36" s="5" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="Q36" s="23" t="n">
         <f aca="false">(H36*$K$6+J36*$K$7+L36*$K$8+N36*$K$9)*$D$8*$D$9</f>
@@ -7826,13 +8159,13 @@
         <v>108</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>23.75</v>
@@ -7868,7 +8201,7 @@
         <v>1</v>
       </c>
       <c r="P37" s="5" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="Q37" s="23" t="n">
         <f aca="false">(H37*$K$6+J37*$K$7+L37*$K$8+N37*$K$9)*$D$8*$D$9</f>
@@ -7928,13 +8261,13 @@
         <v>108</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>22.95</v>
@@ -7970,7 +8303,7 @@
         <v>1</v>
       </c>
       <c r="P38" s="5" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="Q38" s="23" t="n">
         <f aca="false">(H38*$K$6+J38*$K$7+L38*$K$8+N38*$K$9)*$D$8*$D$9</f>
@@ -8030,13 +8363,13 @@
         <v>108</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>15.37</v>
@@ -8072,7 +8405,7 @@
         <v>1</v>
       </c>
       <c r="P39" s="5" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="Q39" s="23" t="n">
         <f aca="false">(H39*$K$6+J39*$K$7+L39*$K$8+N39*$K$9)*$D$8*$D$9</f>
@@ -8132,13 +8465,13 @@
         <v>108</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="E40" s="6" t="n">
         <v>16.26</v>
@@ -8174,7 +8507,7 @@
         <v>1</v>
       </c>
       <c r="P40" s="5" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="Q40" s="23" t="n">
         <f aca="false">(H40*$K$6+J40*$K$7+L40*$K$8+N40*$K$9)*$D$8*$D$9</f>
@@ -8234,13 +8567,13 @@
         <v>108</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="E41" s="6" t="n">
         <v>21.8</v>
@@ -8276,7 +8609,7 @@
         <v>1</v>
       </c>
       <c r="P41" s="5" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="Q41" s="23" t="n">
         <f aca="false">(H41*$K$6+J41*$K$7+L41*$K$8+N41*$K$9)*$D$8*$D$9</f>
@@ -8336,13 +8669,13 @@
         <v>108</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="E42" s="6" t="n">
         <v>24</v>
@@ -8378,7 +8711,7 @@
         <v>1</v>
       </c>
       <c r="P42" s="5" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="Q42" s="23" t="n">
         <f aca="false">(H42*$K$6+J42*$K$7+L42*$K$8+N42*$K$9)*$D$8*$D$9</f>
@@ -8438,13 +8771,13 @@
         <v>108</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="E43" s="6" t="n">
         <v>18.48</v>
@@ -8480,7 +8813,7 @@
         <v>1</v>
       </c>
       <c r="P43" s="5" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="Q43" s="23" t="n">
         <f aca="false">(H43*$K$6+J43*$K$7+L43*$K$8+N43*$K$9)*$D$8*$D$9</f>
@@ -8540,13 +8873,13 @@
         <v>108</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="E44" s="6" t="n">
         <v>24.55</v>
@@ -8582,7 +8915,7 @@
         <v>1</v>
       </c>
       <c r="P44" s="5" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="Q44" s="23" t="n">
         <f aca="false">(H44*$K$6+J44*$K$7+L44*$K$8+N44*$K$9)*$D$8*$D$9</f>
@@ -8642,13 +8975,13 @@
         <v>108</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="E45" s="6" t="n">
         <v>43.05</v>
@@ -8684,7 +9017,7 @@
         <v>1</v>
       </c>
       <c r="P45" s="5" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="Q45" s="23" t="n">
         <f aca="false">(H45*$K$6+J45*$K$7+L45*$K$8+N45*$K$9)*$D$8*$D$9</f>
@@ -8744,13 +9077,13 @@
         <v>108</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="E46" s="6" t="n">
         <v>14.45</v>
@@ -8786,7 +9119,7 @@
         <v>1</v>
       </c>
       <c r="P46" s="5" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="Q46" s="23" t="n">
         <f aca="false">(H46*$K$6+J46*$K$7+L46*$K$8+N46*$K$9)*$D$8*$D$9</f>
@@ -8846,13 +9179,13 @@
         <v>108</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="E47" s="6" t="n">
         <v>42.17</v>
@@ -8888,7 +9221,7 @@
         <v>1</v>
       </c>
       <c r="P47" s="5" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="Q47" s="23" t="n">
         <f aca="false">(H47*$K$6+J47*$K$7+L47*$K$8+N47*$K$9)*$D$8*$D$9</f>
@@ -8948,13 +9281,13 @@
         <v>108</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="E48" s="6" t="n">
         <v>21.92</v>
@@ -8990,7 +9323,7 @@
         <v>1</v>
       </c>
       <c r="P48" s="5" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="Q48" s="23" t="n">
         <f aca="false">(H48*$K$6+J48*$K$7+L48*$K$8+N48*$K$9)*$D$8*$D$9</f>
@@ -9049,7 +9382,7 @@
       <c r="A49" s="13"/>
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="D49" s="13"/>
       <c r="E49" s="13" t="n">
@@ -9122,27 +9455,173 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="16" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="16" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="16" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="16" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="16" t="s">
-        <v>340</v>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="20" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <f aca="false">C59*$D$16</f>
+        <v>114</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <f aca="false">C59*G59</f>
+        <v>342</v>
+      </c>
+      <c r="I59" s="8" t="n">
+        <f aca="false">(D59+F59+H59)*$D$17/1000</f>
+        <v>3.2516</v>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K59" s="4" t="str">
+        <f aca="false">IF(J59&gt;=I59,"UYGUN","KAPASİTE ARTIR")</f>
+        <v>UYGUN</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <f aca="false">C60*$D$16</f>
+        <v>106.2</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <f aca="false">C60*G60</f>
+        <v>318.6</v>
+      </c>
+      <c r="I60" s="8" t="n">
+        <f aca="false">(D60+F60+H60)*$D$17/1000</f>
+        <v>1.56728</v>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K60" s="4" t="str">
+        <f aca="false">IF(J60&gt;=I60,"UYGUN","KAPASİTE ARTIR")</f>
+        <v>UYGUN</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="13"/>
+      <c r="B61" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="15" t="n">
+        <f aca="false">SUM(I59:I60)</f>
+        <v>4.81888</v>
+      </c>
+      <c r="J61" s="28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K61" s="13" t="str">
+        <f aca="false">IF(AND(J61&gt;=I61,J61&gt;=0.9*SUM(J59:J60)),"UYGUN","KONTROL ET")</f>
+        <v>UYGUN</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="16" t="s">
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -9199,7 +9678,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9219,7 +9698,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -9242,49 +9721,49 @@
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>344</v>
+        <v>374</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>345</v>
+        <v>375</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>346</v>
+        <v>376</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>347</v>
+        <v>377</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>349</v>
+        <v>378</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>350</v>
+        <v>379</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>351</v>
+        <v>380</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>352</v>
+        <v>381</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>353</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9292,7 +9771,7 @@
         <v>28</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>120</v>
@@ -9300,7 +9779,7 @@
       <c r="D5" s="7" t="n">
         <v>8.35</v>
       </c>
-      <c r="E5" s="28" t="n">
+      <c r="E5" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB19</f>
         <v>80.766372005988</v>
       </c>
@@ -9308,8 +9787,8 @@
         <f aca="false">'Soğutma Yükü'!AA19</f>
         <v>0.67439920625</v>
       </c>
-      <c r="G5" s="29" t="s">
-        <v>138</v>
+      <c r="G5" s="30" t="s">
+        <v>152</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>1</v>
@@ -9334,12 +9813,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G5,Tablolar!$A$5:$A$10,0))</f>
         <v>50</v>
       </c>
-      <c r="N5" s="30" t="n">
+      <c r="N5" s="31" t="n">
         <f aca="false">H5*M5/1000</f>
         <v>0.05</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="P5" s="5" t="s">
         <v>88</v>
@@ -9350,15 +9829,15 @@
         <v>28</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>42.5</v>
       </c>
-      <c r="E6" s="28" t="n">
+      <c r="E6" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB20</f>
         <v>224.899545588235</v>
       </c>
@@ -9366,8 +9845,8 @@
         <f aca="false">'Soğutma Yükü'!AA20</f>
         <v>9.5582306875</v>
       </c>
-      <c r="G6" s="29" t="s">
-        <v>143</v>
+      <c r="G6" s="30" t="s">
+        <v>157</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>2</v>
@@ -9392,12 +9871,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G6,Tablolar!$A$5:$A$10,0))</f>
         <v>62</v>
       </c>
-      <c r="N6" s="30" t="n">
+      <c r="N6" s="31" t="n">
         <f aca="false">H6*M6/1000</f>
         <v>0.124</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="P6" s="5" t="s">
         <v>88</v>
@@ -9408,15 +9887,15 @@
         <v>28</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>19.7</v>
       </c>
-      <c r="E7" s="28" t="n">
+      <c r="E7" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB21</f>
         <v>131.116880076142</v>
       </c>
@@ -9424,8 +9903,8 @@
         <f aca="false">'Soğutma Yükü'!AA21</f>
         <v>2.5830025375</v>
       </c>
-      <c r="G7" s="29" t="s">
-        <v>145</v>
+      <c r="G7" s="30" t="s">
+        <v>159</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>1</v>
@@ -9450,12 +9929,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G7,Tablolar!$A$5:$A$10,0))</f>
         <v>50</v>
       </c>
-      <c r="N7" s="30" t="n">
+      <c r="N7" s="31" t="n">
         <f aca="false">H7*M7/1000</f>
         <v>0.05</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="P7" s="5" t="s">
         <v>88</v>
@@ -9466,15 +9945,15 @@
         <v>28</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>17.66</v>
       </c>
-      <c r="E8" s="28" t="n">
+      <c r="E8" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB22</f>
         <v>114.462734569649</v>
       </c>
@@ -9482,8 +9961,8 @@
         <f aca="false">'Soğutma Yükü'!AA22</f>
         <v>2.0214118925</v>
       </c>
-      <c r="G8" s="29" t="s">
-        <v>138</v>
+      <c r="G8" s="30" t="s">
+        <v>152</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>1</v>
@@ -9508,12 +9987,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G8,Tablolar!$A$5:$A$10,0))</f>
         <v>50</v>
       </c>
-      <c r="N8" s="30" t="n">
+      <c r="N8" s="31" t="n">
         <f aca="false">H8*M8/1000</f>
         <v>0.05</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="P8" s="5" t="s">
         <v>88</v>
@@ -9524,15 +10003,15 @@
         <v>28</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>22.15</v>
       </c>
-      <c r="E9" s="28" t="n">
+      <c r="E9" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB23</f>
         <v>101.418631207675</v>
       </c>
@@ -9540,8 +10019,8 @@
         <f aca="false">'Soğutma Yükü'!AA23</f>
         <v>2.24642268125</v>
       </c>
-      <c r="G9" s="29" t="s">
-        <v>145</v>
+      <c r="G9" s="30" t="s">
+        <v>159</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>1</v>
@@ -9566,12 +10045,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G9,Tablolar!$A$5:$A$10,0))</f>
         <v>50</v>
       </c>
-      <c r="N9" s="30" t="n">
+      <c r="N9" s="31" t="n">
         <f aca="false">H9*M9/1000</f>
         <v>0.05</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="P9" s="5" t="s">
         <v>88</v>
@@ -9582,15 +10061,15 @@
         <v>28</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>16.07</v>
       </c>
-      <c r="E10" s="28" t="n">
+      <c r="E10" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB24</f>
         <v>119.292504122589</v>
       </c>
@@ -9598,8 +10077,8 @@
         <f aca="false">'Soğutma Yükü'!AA24</f>
         <v>1.91703054125</v>
       </c>
-      <c r="G10" s="29" t="s">
-        <v>138</v>
+      <c r="G10" s="30" t="s">
+        <v>152</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>1</v>
@@ -9624,12 +10103,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G10,Tablolar!$A$5:$A$10,0))</f>
         <v>50</v>
       </c>
-      <c r="N10" s="30" t="n">
+      <c r="N10" s="31" t="n">
         <f aca="false">H10*M10/1000</f>
         <v>0.05</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="P10" s="5" t="s">
         <v>88</v>
@@ -9640,15 +10119,15 @@
         <v>28</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>16.4</v>
       </c>
-      <c r="E11" s="28" t="n">
+      <c r="E11" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB25</f>
         <v>178.212375</v>
       </c>
@@ -9656,8 +10135,8 @@
         <f aca="false">'Soğutma Yükü'!AA25</f>
         <v>2.92268295</v>
       </c>
-      <c r="G11" s="29" t="s">
-        <v>147</v>
+      <c r="G11" s="30" t="s">
+        <v>161</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>1</v>
@@ -9682,12 +10161,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G11,Tablolar!$A$5:$A$10,0))</f>
         <v>60</v>
       </c>
-      <c r="N11" s="30" t="n">
+      <c r="N11" s="31" t="n">
         <f aca="false">H11*M11/1000</f>
         <v>0.06</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="P11" s="5" t="s">
         <v>88</v>
@@ -9698,15 +10177,15 @@
         <v>103</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>42.65</v>
       </c>
-      <c r="E12" s="28" t="n">
+      <c r="E12" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB26</f>
         <v>117.220863276671</v>
       </c>
@@ -9714,8 +10193,8 @@
         <f aca="false">'Soğutma Yükü'!AA26</f>
         <v>4.99946981875</v>
       </c>
-      <c r="G12" s="29" t="s">
-        <v>145</v>
+      <c r="G12" s="30" t="s">
+        <v>159</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>2</v>
@@ -9740,12 +10219,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G12,Tablolar!$A$5:$A$10,0))</f>
         <v>50</v>
       </c>
-      <c r="N12" s="30" t="n">
+      <c r="N12" s="31" t="n">
         <f aca="false">H12*M12/1000</f>
         <v>0.1</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="P12" s="5" t="s">
         <v>104</v>
@@ -9756,15 +10235,15 @@
         <v>103</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>43.8</v>
       </c>
-      <c r="E13" s="28" t="n">
+      <c r="E13" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB27</f>
         <v>118.040591894977</v>
       </c>
@@ -9772,8 +10251,8 @@
         <f aca="false">'Soğutma Yükü'!AA27</f>
         <v>5.170177925</v>
       </c>
-      <c r="G13" s="29" t="s">
-        <v>145</v>
+      <c r="G13" s="30" t="s">
+        <v>159</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>2</v>
@@ -9798,12 +10277,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G13,Tablolar!$A$5:$A$10,0))</f>
         <v>50</v>
       </c>
-      <c r="N13" s="30" t="n">
+      <c r="N13" s="31" t="n">
         <f aca="false">H13*M13/1000</f>
         <v>0.1</v>
       </c>
       <c r="O13" s="5" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="P13" s="5" t="s">
         <v>104</v>
@@ -9814,15 +10293,15 @@
         <v>103</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>27.5</v>
       </c>
-      <c r="E14" s="28" t="n">
+      <c r="E14" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB28</f>
         <v>99.583355</v>
       </c>
@@ -9830,8 +10309,8 @@
         <f aca="false">'Soğutma Yükü'!AA28</f>
         <v>2.7385422625</v>
       </c>
-      <c r="G14" s="29" t="s">
-        <v>145</v>
+      <c r="G14" s="30" t="s">
+        <v>159</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>1</v>
@@ -9856,12 +10335,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G14,Tablolar!$A$5:$A$10,0))</f>
         <v>50</v>
       </c>
-      <c r="N14" s="30" t="n">
+      <c r="N14" s="31" t="n">
         <f aca="false">H14*M14/1000</f>
         <v>0.05</v>
       </c>
       <c r="O14" s="5" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="P14" s="5" t="s">
         <v>104</v>
@@ -9872,15 +10351,15 @@
         <v>103</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>24.15</v>
       </c>
-      <c r="E15" s="28" t="n">
+      <c r="E15" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB29</f>
         <v>167.973458850932</v>
       </c>
@@ -9888,8 +10367,8 @@
         <f aca="false">'Soğutma Yükü'!AA29</f>
         <v>4.05655903125</v>
       </c>
-      <c r="G15" s="29" t="s">
-        <v>150</v>
+      <c r="G15" s="30" t="s">
+        <v>164</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>1</v>
@@ -9914,12 +10393,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G15,Tablolar!$A$5:$A$10,0))</f>
         <v>60</v>
       </c>
-      <c r="N15" s="30" t="n">
+      <c r="N15" s="31" t="n">
         <f aca="false">H15*M15/1000</f>
         <v>0.06</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="P15" s="5" t="s">
         <v>104</v>
@@ -9930,15 +10409,15 @@
         <v>103</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E16" s="28" t="n">
+      <c r="E16" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB30</f>
         <v>174.725475917431</v>
       </c>
@@ -9946,8 +10425,8 @@
         <f aca="false">'Soğutma Yükü'!AA30</f>
         <v>3.809015375</v>
       </c>
-      <c r="G16" s="29" t="s">
-        <v>150</v>
+      <c r="G16" s="30" t="s">
+        <v>164</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>1</v>
@@ -9972,12 +10451,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G16,Tablolar!$A$5:$A$10,0))</f>
         <v>60</v>
       </c>
-      <c r="N16" s="30" t="n">
+      <c r="N16" s="31" t="n">
         <f aca="false">H16*M16/1000</f>
         <v>0.06</v>
       </c>
       <c r="O16" s="5" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="P16" s="5" t="s">
         <v>104</v>
@@ -9988,15 +10467,15 @@
         <v>103</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="E17" s="28" t="n">
+      <c r="E17" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB31</f>
         <v>147.535666666667</v>
       </c>
@@ -10004,8 +10483,8 @@
         <f aca="false">'Soğutma Yükü'!AA31</f>
         <v>3.540856</v>
       </c>
-      <c r="G17" s="29" t="s">
-        <v>147</v>
+      <c r="G17" s="30" t="s">
+        <v>161</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>1</v>
@@ -10030,12 +10509,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G17,Tablolar!$A$5:$A$10,0))</f>
         <v>60</v>
       </c>
-      <c r="N17" s="30" t="n">
+      <c r="N17" s="31" t="n">
         <f aca="false">H17*M17/1000</f>
         <v>0.06</v>
       </c>
       <c r="O17" s="5" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="P17" s="5" t="s">
         <v>104</v>
@@ -10046,15 +10525,15 @@
         <v>103</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>19.48</v>
       </c>
-      <c r="E18" s="28" t="n">
+      <c r="E18" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB32</f>
         <v>109.490722022587</v>
       </c>
@@ -10062,8 +10541,8 @@
         <f aca="false">'Soğutma Yükü'!AA32</f>
         <v>2.132879265</v>
       </c>
-      <c r="G18" s="29" t="s">
-        <v>138</v>
+      <c r="G18" s="30" t="s">
+        <v>152</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>1</v>
@@ -10088,12 +10567,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G18,Tablolar!$A$5:$A$10,0))</f>
         <v>50</v>
       </c>
-      <c r="N18" s="30" t="n">
+      <c r="N18" s="31" t="n">
         <f aca="false">H18*M18/1000</f>
         <v>0.05</v>
       </c>
       <c r="O18" s="5" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="P18" s="5" t="s">
         <v>104</v>
@@ -10104,15 +10583,15 @@
         <v>103</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D19" s="7" t="n">
         <v>24.53</v>
       </c>
-      <c r="E19" s="28" t="n">
+      <c r="E19" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB33</f>
         <v>145.160166479821</v>
       </c>
@@ -10120,8 +10599,8 @@
         <f aca="false">'Soğutma Yükü'!AA33</f>
         <v>3.56077888375</v>
       </c>
-      <c r="G19" s="29" t="s">
-        <v>147</v>
+      <c r="G19" s="30" t="s">
+        <v>161</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>1</v>
@@ -10146,12 +10625,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G19,Tablolar!$A$5:$A$10,0))</f>
         <v>60</v>
       </c>
-      <c r="N19" s="30" t="n">
+      <c r="N19" s="31" t="n">
         <f aca="false">H19*M19/1000</f>
         <v>0.06</v>
       </c>
       <c r="O19" s="5" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="P19" s="5" t="s">
         <v>104</v>
@@ -10162,15 +10641,15 @@
         <v>103</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>39.9</v>
       </c>
-      <c r="E20" s="28" t="n">
+      <c r="E20" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB34</f>
         <v>135.125113095238</v>
       </c>
@@ -10178,8 +10657,8 @@
         <f aca="false">'Soğutma Yükü'!AA34</f>
         <v>5.3914920125</v>
       </c>
-      <c r="G20" s="29" t="s">
-        <v>145</v>
+      <c r="G20" s="30" t="s">
+        <v>159</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>2</v>
@@ -10204,12 +10683,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G20,Tablolar!$A$5:$A$10,0))</f>
         <v>50</v>
       </c>
-      <c r="N20" s="30" t="n">
+      <c r="N20" s="31" t="n">
         <f aca="false">H20*M20/1000</f>
         <v>0.1</v>
       </c>
       <c r="O20" s="5" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="P20" s="5" t="s">
         <v>104</v>
@@ -10220,15 +10699,15 @@
         <v>103</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>39.65</v>
       </c>
-      <c r="E21" s="28" t="n">
+      <c r="E21" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB35</f>
         <v>142.448801860025</v>
       </c>
@@ -10236,8 +10715,8 @@
         <f aca="false">'Soğutma Yükü'!AA35</f>
         <v>5.64809499375</v>
       </c>
-      <c r="G21" s="29" t="s">
-        <v>147</v>
+      <c r="G21" s="30" t="s">
+        <v>161</v>
       </c>
       <c r="H21" s="6" t="n">
         <v>2</v>
@@ -10262,12 +10741,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G21,Tablolar!$A$5:$A$10,0))</f>
         <v>60</v>
       </c>
-      <c r="N21" s="30" t="n">
+      <c r="N21" s="31" t="n">
         <f aca="false">H21*M21/1000</f>
         <v>0.12</v>
       </c>
       <c r="O21" s="5" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="P21" s="5" t="s">
         <v>104</v>
@@ -10278,15 +10757,15 @@
         <v>108</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="E22" s="28" t="n">
+      <c r="E22" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB36</f>
         <v>143.692175</v>
       </c>
@@ -10294,8 +10773,8 @@
         <f aca="false">'Soğutma Yükü'!AA36</f>
         <v>3.4486122</v>
       </c>
-      <c r="G22" s="29" t="s">
-        <v>147</v>
+      <c r="G22" s="30" t="s">
+        <v>161</v>
       </c>
       <c r="H22" s="6" t="n">
         <v>1</v>
@@ -10320,12 +10799,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G22,Tablolar!$A$5:$A$10,0))</f>
         <v>60</v>
       </c>
-      <c r="N22" s="30" t="n">
+      <c r="N22" s="31" t="n">
         <f aca="false">H22*M22/1000</f>
         <v>0.06</v>
       </c>
       <c r="O22" s="5" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="P22" s="5" t="s">
         <v>109</v>
@@ -10336,15 +10815,15 @@
         <v>108</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>23.75</v>
       </c>
-      <c r="E23" s="28" t="n">
+      <c r="E23" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB37</f>
         <v>136.576483421053</v>
       </c>
@@ -10352,8 +10831,8 @@
         <f aca="false">'Soğutma Yükü'!AA37</f>
         <v>3.24369148125</v>
       </c>
-      <c r="G23" s="29" t="s">
-        <v>147</v>
+      <c r="G23" s="30" t="s">
+        <v>161</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>1</v>
@@ -10378,12 +10857,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G23,Tablolar!$A$5:$A$10,0))</f>
         <v>60</v>
       </c>
-      <c r="N23" s="30" t="n">
+      <c r="N23" s="31" t="n">
         <f aca="false">H23*M23/1000</f>
         <v>0.06</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="P23" s="5" t="s">
         <v>109</v>
@@ -10394,15 +10873,15 @@
         <v>108</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>22.95</v>
       </c>
-      <c r="E24" s="28" t="n">
+      <c r="E24" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB38</f>
         <v>139.517454520697</v>
       </c>
@@ -10410,8 +10889,8 @@
         <f aca="false">'Soğutma Yükü'!AA38</f>
         <v>3.20192558125</v>
       </c>
-      <c r="G24" s="29" t="s">
-        <v>147</v>
+      <c r="G24" s="30" t="s">
+        <v>161</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>1</v>
@@ -10436,12 +10915,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G24,Tablolar!$A$5:$A$10,0))</f>
         <v>60</v>
       </c>
-      <c r="N24" s="30" t="n">
+      <c r="N24" s="31" t="n">
         <f aca="false">H24*M24/1000</f>
         <v>0.06</v>
       </c>
       <c r="O24" s="5" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="P24" s="5" t="s">
         <v>109</v>
@@ -10452,15 +10931,15 @@
         <v>108</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>15.37</v>
       </c>
-      <c r="E25" s="28" t="n">
+      <c r="E25" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB39</f>
         <v>224.490008376708</v>
       </c>
@@ -10468,8 +10947,8 @@
         <f aca="false">'Soğutma Yükü'!AA39</f>
         <v>3.45041142875</v>
       </c>
-      <c r="G25" s="29" t="s">
-        <v>147</v>
+      <c r="G25" s="30" t="s">
+        <v>161</v>
       </c>
       <c r="H25" s="6" t="n">
         <v>1</v>
@@ -10494,12 +10973,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G25,Tablolar!$A$5:$A$10,0))</f>
         <v>60</v>
       </c>
-      <c r="N25" s="30" t="n">
+      <c r="N25" s="31" t="n">
         <f aca="false">H25*M25/1000</f>
         <v>0.06</v>
       </c>
       <c r="O25" s="5" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="P25" s="5" t="s">
         <v>109</v>
@@ -10510,15 +10989,15 @@
         <v>108</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>16.26</v>
       </c>
-      <c r="E26" s="28" t="n">
+      <c r="E26" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB40</f>
         <v>208.121787669127</v>
       </c>
@@ -10526,8 +11005,8 @@
         <f aca="false">'Soğutma Yükü'!AA40</f>
         <v>3.3840602675</v>
       </c>
-      <c r="G26" s="29" t="s">
-        <v>147</v>
+      <c r="G26" s="30" t="s">
+        <v>161</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>1</v>
@@ -10552,12 +11031,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G26,Tablolar!$A$5:$A$10,0))</f>
         <v>60</v>
       </c>
-      <c r="N26" s="30" t="n">
+      <c r="N26" s="31" t="n">
         <f aca="false">H26*M26/1000</f>
         <v>0.06</v>
       </c>
       <c r="O26" s="5" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="P26" s="5" t="s">
         <v>109</v>
@@ -10568,15 +11047,15 @@
         <v>108</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E27" s="28" t="n">
+      <c r="E27" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB41</f>
         <v>184.405475917431</v>
       </c>
@@ -10584,8 +11063,8 @@
         <f aca="false">'Soğutma Yükü'!AA41</f>
         <v>4.020039375</v>
       </c>
-      <c r="G27" s="29" t="s">
-        <v>150</v>
+      <c r="G27" s="30" t="s">
+        <v>164</v>
       </c>
       <c r="H27" s="6" t="n">
         <v>1</v>
@@ -10610,12 +11089,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G27,Tablolar!$A$5:$A$10,0))</f>
         <v>60</v>
       </c>
-      <c r="N27" s="30" t="n">
+      <c r="N27" s="31" t="n">
         <f aca="false">H27*M27/1000</f>
         <v>0.06</v>
       </c>
       <c r="O27" s="5" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="P27" s="5" t="s">
         <v>109</v>
@@ -10626,15 +11105,15 @@
         <v>108</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="E28" s="28" t="n">
+      <c r="E28" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB42</f>
         <v>157.215666666667</v>
       </c>
@@ -10642,8 +11121,8 @@
         <f aca="false">'Soğutma Yükü'!AA42</f>
         <v>3.773176</v>
       </c>
-      <c r="G28" s="29" t="s">
-        <v>150</v>
+      <c r="G28" s="30" t="s">
+        <v>164</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>1</v>
@@ -10668,12 +11147,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G28,Tablolar!$A$5:$A$10,0))</f>
         <v>60</v>
       </c>
-      <c r="N28" s="30" t="n">
+      <c r="N28" s="31" t="n">
         <f aca="false">H28*M28/1000</f>
         <v>0.06</v>
       </c>
       <c r="O28" s="5" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="P28" s="5" t="s">
         <v>109</v>
@@ -10684,15 +11163,15 @@
         <v>108</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>18.48</v>
       </c>
-      <c r="E29" s="28" t="n">
+      <c r="E29" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB43</f>
         <v>123.173744047619</v>
       </c>
@@ -10700,8 +11179,8 @@
         <f aca="false">'Soğutma Yükü'!AA43</f>
         <v>2.27625079</v>
       </c>
-      <c r="G29" s="29" t="s">
-        <v>145</v>
+      <c r="G29" s="30" t="s">
+        <v>159</v>
       </c>
       <c r="H29" s="6" t="n">
         <v>1</v>
@@ -10726,12 +11205,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G29,Tablolar!$A$5:$A$10,0))</f>
         <v>50</v>
       </c>
-      <c r="N29" s="30" t="n">
+      <c r="N29" s="31" t="n">
         <f aca="false">H29*M29/1000</f>
         <v>0.05</v>
       </c>
       <c r="O29" s="5" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="P29" s="5" t="s">
         <v>109</v>
@@ -10742,15 +11221,15 @@
         <v>108</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>24.55</v>
       </c>
-      <c r="E30" s="28" t="n">
+      <c r="E30" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB44</f>
         <v>154.750842413442</v>
       </c>
@@ -10758,8 +11237,8 @@
         <f aca="false">'Soğutma Yükü'!AA44</f>
         <v>3.79913318125</v>
       </c>
-      <c r="G30" s="29" t="s">
-        <v>150</v>
+      <c r="G30" s="30" t="s">
+        <v>164</v>
       </c>
       <c r="H30" s="6" t="n">
         <v>1</v>
@@ -10784,12 +11263,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G30,Tablolar!$A$5:$A$10,0))</f>
         <v>60</v>
       </c>
-      <c r="N30" s="30" t="n">
+      <c r="N30" s="31" t="n">
         <f aca="false">H30*M30/1000</f>
         <v>0.06</v>
       </c>
       <c r="O30" s="5" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="P30" s="5" t="s">
         <v>109</v>
@@ -10800,15 +11279,15 @@
         <v>108</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="D31" s="7" t="n">
         <v>43.05</v>
       </c>
-      <c r="E31" s="28" t="n">
+      <c r="E31" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB45</f>
         <v>131.505908681765</v>
       </c>
@@ -10816,8 +11295,8 @@
         <f aca="false">'Soğutma Yükü'!AA45</f>
         <v>5.66132936875</v>
       </c>
-      <c r="G31" s="29" t="s">
-        <v>147</v>
+      <c r="G31" s="30" t="s">
+        <v>161</v>
       </c>
       <c r="H31" s="6" t="n">
         <v>2</v>
@@ -10842,12 +11321,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G31,Tablolar!$A$5:$A$10,0))</f>
         <v>60</v>
       </c>
-      <c r="N31" s="30" t="n">
+      <c r="N31" s="31" t="n">
         <f aca="false">H31*M31/1000</f>
         <v>0.12</v>
       </c>
       <c r="O31" s="5" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="P31" s="5" t="s">
         <v>109</v>
@@ -10858,15 +11337,15 @@
         <v>108</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>14.45</v>
       </c>
-      <c r="E32" s="28" t="n">
+      <c r="E32" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB46</f>
         <v>159.099684688581</v>
       </c>
@@ -10874,8 +11353,8 @@
         <f aca="false">'Soğutma Yükü'!AA46</f>
         <v>2.29899044375</v>
       </c>
-      <c r="G32" s="29" t="s">
-        <v>145</v>
+      <c r="G32" s="30" t="s">
+        <v>159</v>
       </c>
       <c r="H32" s="6" t="n">
         <v>1</v>
@@ -10900,12 +11379,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G32,Tablolar!$A$5:$A$10,0))</f>
         <v>50</v>
       </c>
-      <c r="N32" s="30" t="n">
+      <c r="N32" s="31" t="n">
         <f aca="false">H32*M32/1000</f>
         <v>0.05</v>
       </c>
       <c r="O32" s="5" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="P32" s="5" t="s">
         <v>109</v>
@@ -10916,15 +11395,15 @@
         <v>108</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="D33" s="7" t="n">
         <v>42.17</v>
       </c>
-      <c r="E33" s="28" t="n">
+      <c r="E33" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB47</f>
         <v>146.43387191724</v>
       </c>
@@ -10932,8 +11411,8 @@
         <f aca="false">'Soğutma Yükü'!AA47</f>
         <v>6.17511637875</v>
       </c>
-      <c r="G33" s="29" t="s">
-        <v>147</v>
+      <c r="G33" s="30" t="s">
+        <v>161</v>
       </c>
       <c r="H33" s="6" t="n">
         <v>2</v>
@@ -10958,12 +11437,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G33,Tablolar!$A$5:$A$10,0))</f>
         <v>60</v>
       </c>
-      <c r="N33" s="30" t="n">
+      <c r="N33" s="31" t="n">
         <f aca="false">H33*M33/1000</f>
         <v>0.12</v>
       </c>
       <c r="O33" s="5" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="P33" s="5" t="s">
         <v>109</v>
@@ -10974,15 +11453,15 @@
         <v>108</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>21.92</v>
       </c>
-      <c r="E34" s="28" t="n">
+      <c r="E34" s="29" t="n">
         <f aca="false">'Soğutma Yükü'!AB48</f>
         <v>200.298739051095</v>
       </c>
@@ -10990,8 +11469,8 @@
         <f aca="false">'Soğutma Yükü'!AA48</f>
         <v>4.39054836</v>
       </c>
-      <c r="G34" s="29" t="s">
-        <v>150</v>
+      <c r="G34" s="30" t="s">
+        <v>164</v>
       </c>
       <c r="H34" s="6" t="n">
         <v>1</v>
@@ -11016,12 +11495,12 @@
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(G34,Tablolar!$A$5:$A$10,0))</f>
         <v>60</v>
       </c>
-      <c r="N34" s="30" t="n">
+      <c r="N34" s="31" t="n">
         <f aca="false">H34*M34/1000</f>
         <v>0.06</v>
       </c>
       <c r="O34" s="5" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="P34" s="5" t="s">
         <v>109</v>
@@ -11031,7 +11510,7 @@
       <c r="A35" s="13"/>
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="D35" s="15" t="n">
         <f aca="false">SUM(D5:D34)</f>
@@ -11058,7 +11537,7 @@
         <v>143.8</v>
       </c>
       <c r="M35" s="13"/>
-      <c r="N35" s="31" t="n">
+      <c r="N35" s="32" t="n">
         <f aca="false">SUM(N5:N34)</f>
         <v>2.074</v>
       </c>
@@ -11067,12 +11546,12 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
-        <v>356</v>
+        <v>385</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="16" t="s">
-        <v>357</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -11111,7 +11590,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>358</v>
+        <v>387</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11126,7 +11605,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>359</v>
+        <v>388</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11144,42 +11623,42 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>360</v>
+        <v>389</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>361</v>
+        <v>390</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>362</v>
+        <v>391</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>363</v>
+        <v>392</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>364</v>
+        <v>393</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>365</v>
+        <v>394</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>366</v>
+        <v>395</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>367</v>
+        <v>396</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>368</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>12</v>
@@ -11191,13 +11670,13 @@
         <v>13.8</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>370</v>
+        <v>399</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>371</v>
+        <v>400</v>
       </c>
       <c r="I5" s="8" t="n">
         <f aca="false">SUMIF('VRF İç Üniteler'!$O$5:$O$34,A5,'VRF İç Üniteler'!$J$5:$J$34)</f>
@@ -11207,17 +11686,17 @@
         <f aca="false">SUMIF($A$5:$A$7,A5,$D$5:$D$7)</f>
         <v>67</v>
       </c>
-      <c r="K5" s="32" t="n">
+      <c r="K5" s="33" t="n">
         <f aca="false">IF(J5=0,0,I5/J5)</f>
         <v>1.07761194029851</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>12</v>
@@ -11229,13 +11708,13 @@
         <v>13.8</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>370</v>
+        <v>399</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>371</v>
+        <v>400</v>
       </c>
       <c r="I6" s="8" t="n">
         <f aca="false">SUMIF('VRF İç Üniteler'!$O$5:$O$34,A6,'VRF İç Üniteler'!$J$5:$J$34)</f>
@@ -11245,17 +11724,17 @@
         <f aca="false">SUMIF($A$5:$A$7,A6,$D$5:$D$7)</f>
         <v>67</v>
       </c>
-      <c r="K6" s="32" t="n">
+      <c r="K6" s="33" t="n">
         <f aca="false">IF(J6=0,0,I6/J6)</f>
         <v>1.07761194029851</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>18</v>
@@ -11267,13 +11746,13 @@
         <v>21</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>370</v>
+        <v>399</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>372</v>
+        <v>401</v>
       </c>
       <c r="I7" s="8" t="n">
         <f aca="false">SUMIF('VRF İç Üniteler'!$O$5:$O$34,A7,'VRF İç Üniteler'!$J$5:$J$34)</f>
@@ -11283,7 +11762,7 @@
         <f aca="false">SUMIF($A$5:$A$7,A7,$D$5:$D$7)</f>
         <v>50</v>
       </c>
-      <c r="K7" s="32" t="n">
+      <c r="K7" s="33" t="n">
         <f aca="false">IF(J7=0,0,I7/J7)</f>
         <v>1.12</v>
       </c>
@@ -11291,7 +11770,7 @@
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13"/>
       <c r="B8" s="14" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="C8" s="13" t="n">
         <f aca="false">SUM(C5:C7)</f>
@@ -11314,17 +11793,17 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>373</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>374</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>375</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>

--- a/mekanik-elektrik/TMO_MARDIN_MEKANIK_EKIPMAN_ELEKTRIK_GUCLERI.xlsx
+++ b/mekanik-elektrik/TMO_MARDIN_MEKANIK_EKIPMAN_ELEKTRIK_GUCLERI.xlsx
@@ -16,7 +16,7 @@
     <sheet name="VRF Dış Üniteler" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Elektrik Güç Tablosu'!$A$4:$U$42</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Elektrik Güç Tablosu'!$A$4:$U$44</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="416">
   <si>
     <t xml:space="preserve">MEKANİK EKİPMAN ELEKTRİK GÜÇ TABLOSU</t>
   </si>
@@ -277,6 +277,36 @@
     <t xml:space="preserve">Edirne yağmur suyu (1-1,5 kW)</t>
   </si>
   <si>
+    <t xml:space="preserve">YGP-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YANGIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elektrik Motorlu Ana Yangın Pompası</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT1 sprinkler 12 x 60 lt/dk = 43,2 m³/h + 1 yangın dolabı 6 m³/h: Q=50 m³/h, Hm=80 mSS, 2900 d/d, yıldız-üçgen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YNG-P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT1: 12 sprinkler x (5 lt/dk.m² x 12 m²) + dolap 100 lt/dk; Hm=80 mSS (Edirne: 50-59 m³/h, 80 mSS, 20 kW)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JP-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jokey (Basınç Tamamlama) Pompası</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q=2 m³/h, Hm=85 mSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edirne yangın pompa grubu eşdeğeri</t>
+  </si>
+  <si>
     <t xml:space="preserve">EF-01</t>
   </si>
   <si>
@@ -593,6 +623,9 @@
   </si>
   <si>
     <t xml:space="preserve">Pay (Talep)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yangın Pompa Panosu (ana şalterden önce / jeneratör beslemeli)</t>
   </si>
   <si>
     <t xml:space="preserve">Mekanik Pano - Teshin Merkezi (ısıtma, hidrofor, yağmur suyu, teshin fanları)</t>
@@ -1889,7 +1922,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:U58"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -2796,7 +2829,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
@@ -2813,7 +2846,7 @@
         <v>78</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>28</v>
@@ -2825,65 +2858,65 @@
         <v>1</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>0.2</v>
+        <v>22</v>
       </c>
       <c r="K16" s="8" t="n">
         <f aca="false">H16*J16</f>
-        <v>0.2</v>
+        <v>22</v>
       </c>
       <c r="L16" s="8" t="n">
         <f aca="false">I16*J16</f>
-        <v>0.2</v>
+        <v>22</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>230</v>
+        <v>400</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="P16" s="8" t="n">
         <f aca="false">IF(OR(J16=0,M16=0),0,IF(N16=3,J16*1000/(SQRT(3)*M16*O16),J16*1000/(M16*O16)))</f>
-        <v>1.0230179028133</v>
+        <v>36.0843918243516</v>
       </c>
       <c r="Q16" s="4" t="n">
         <f aca="false">IF(P16=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P16*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="R16" s="4" t="str">
         <f aca="false">IF(P16=0,"-",IF(N16=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P16*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
-        <v>3x2,5 mm²</v>
+        <v>5x10 mm²</v>
       </c>
       <c r="S16" s="5" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="T16" s="5" t="s">
         <v>30</v>
       </c>
       <c r="U16" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>28</v>
@@ -2895,28 +2928,28 @@
         <v>1</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="K17" s="8" t="n">
         <f aca="false">H17*J17</f>
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="L17" s="8" t="n">
         <f aca="false">I17*J17</f>
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>230</v>
+        <v>400</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O17" s="7" t="n">
         <v>0.85</v>
       </c>
       <c r="P17" s="8" t="n">
         <f aca="false">IF(OR(J17=0,M17=0),0,IF(N17=3,J17*1000/(SQRT(3)*M17*O17),J17*1000/(M17*O17)))</f>
-        <v>1.0230179028133</v>
+        <v>3.73579585946228</v>
       </c>
       <c r="Q17" s="4" t="n">
         <f aca="false">IF(P17=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P17*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
@@ -2924,16 +2957,16 @@
       </c>
       <c r="R17" s="4" t="str">
         <f aca="false">IF(P17=0,"-",IF(N17=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P17*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
-        <v>3x2,5 mm²</v>
+        <v>5x2,5 mm²</v>
       </c>
       <c r="S17" s="5" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="T17" s="5" t="s">
         <v>30</v>
       </c>
       <c r="U17" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2941,19 +2974,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>28</v>
@@ -2997,7 +3030,7 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S18" s="5" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="T18" s="5" t="s">
         <v>30</v>
@@ -3006,7 +3039,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
@@ -3014,7 +3047,7 @@
         <v>90</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>91</v>
@@ -3023,7 +3056,7 @@
         <v>92</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>28</v>
@@ -3067,13 +3100,13 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S19" s="5" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="T19" s="5" t="s">
         <v>30</v>
       </c>
       <c r="U19" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3081,19 +3114,19 @@
         <v>16</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="F20" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>28</v>
@@ -3137,7 +3170,7 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S20" s="5" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="T20" s="5" t="s">
         <v>30</v>
@@ -3146,7 +3179,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
@@ -3154,7 +3187,7 @@
         <v>100</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>101</v>
@@ -3163,10 +3196,10 @@
         <v>102</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="H21" s="6" t="n">
         <v>1</v>
@@ -3175,15 +3208,15 @@
         <v>1</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="K21" s="8" t="n">
         <f aca="false">H21*J21</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="L21" s="8" t="n">
         <f aca="false">I21*J21</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M21" s="6" t="n">
         <v>230</v>
@@ -3196,7 +3229,7 @@
       </c>
       <c r="P21" s="8" t="n">
         <f aca="false">IF(OR(J21=0,M21=0),0,IF(N21=3,J21*1000/(SQRT(3)*M21*O21),J21*1000/(M21*O21)))</f>
-        <v>1.27877237851662</v>
+        <v>1.0230179028133</v>
       </c>
       <c r="Q21" s="4" t="n">
         <f aca="false">IF(P21=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P21*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
@@ -3207,13 +3240,13 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S21" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="T21" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="U21" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="T21" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="U21" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3221,22 +3254,22 @@
         <v>18</v>
       </c>
       <c r="B22" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" s="5" t="s">
+      <c r="E22" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>102</v>
-      </c>
       <c r="F22" s="5" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="H22" s="6" t="n">
         <v>1</v>
@@ -3245,15 +3278,15 @@
         <v>1</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="K22" s="8" t="n">
         <f aca="false">H22*J22</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="L22" s="8" t="n">
         <f aca="false">I22*J22</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M22" s="6" t="n">
         <v>230</v>
@@ -3266,7 +3299,7 @@
       </c>
       <c r="P22" s="8" t="n">
         <f aca="false">IF(OR(J22=0,M22=0),0,IF(N22=3,J22*1000/(SQRT(3)*M22*O22),J22*1000/(M22*O22)))</f>
-        <v>1.27877237851662</v>
+        <v>1.0230179028133</v>
       </c>
       <c r="Q22" s="4" t="n">
         <f aca="false">IF(P22=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P22*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
@@ -3277,13 +3310,13 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S22" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="T22" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="U22" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="T22" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="U22" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3291,23 +3324,23 @@
         <v>19</v>
       </c>
       <c r="B23" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="F23" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>108</v>
-      </c>
       <c r="H23" s="6" t="n">
         <v>1</v>
       </c>
@@ -3315,15 +3348,15 @@
         <v>1</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="K23" s="8" t="n">
         <f aca="false">H23*J23</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="L23" s="8" t="n">
         <f aca="false">I23*J23</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="M23" s="6" t="n">
         <v>230</v>
@@ -3336,7 +3369,7 @@
       </c>
       <c r="P23" s="8" t="n">
         <f aca="false">IF(OR(J23=0,M23=0),0,IF(N23=3,J23*1000/(SQRT(3)*M23*O23),J23*1000/(M23*O23)))</f>
-        <v>1.0230179028133</v>
+        <v>1.27877237851662</v>
       </c>
       <c r="Q23" s="4" t="n">
         <f aca="false">IF(P23=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P23*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
@@ -3347,13 +3380,13 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S23" s="5" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="T23" s="5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="U23" s="5" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3364,20 +3397,20 @@
         <v>116</v>
       </c>
       <c r="C24" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="E24" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="H24" s="6" t="n">
         <v>1</v>
       </c>
@@ -3385,15 +3418,15 @@
         <v>1</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>0.02</v>
+        <v>0.25</v>
       </c>
       <c r="K24" s="8" t="n">
         <f aca="false">H24*J24</f>
-        <v>0.02</v>
+        <v>0.25</v>
       </c>
       <c r="L24" s="8" t="n">
         <f aca="false">I24*J24</f>
-        <v>0.02</v>
+        <v>0.25</v>
       </c>
       <c r="M24" s="6" t="n">
         <v>230</v>
@@ -3402,11 +3435,11 @@
         <v>1</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="P24" s="8" t="n">
         <f aca="false">IF(OR(J24=0,M24=0),0,IF(N24=3,J24*1000/(SQRT(3)*M24*O24),J24*1000/(M24*O24)))</f>
-        <v>0.0966183574879227</v>
+        <v>1.27877237851662</v>
       </c>
       <c r="Q24" s="4" t="n">
         <f aca="false">IF(P24=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P24*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
@@ -3417,36 +3450,36 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S24" s="5" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="T24" s="5" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="U24" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="n">
         <v>21</v>
       </c>
       <c r="B25" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="F25" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="F25" s="5" t="s">
-        <v>125</v>
-      </c>
       <c r="G25" s="5" t="s">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="H25" s="6" t="n">
         <v>1</v>
@@ -3455,15 +3488,15 @@
         <v>1</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="K25" s="8" t="n">
         <f aca="false">H25*J25</f>
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="L25" s="8" t="n">
         <f aca="false">I25*J25</f>
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="M25" s="6" t="n">
         <v>230</v>
@@ -3472,48 +3505,48 @@
         <v>1</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="P25" s="8" t="n">
         <f aca="false">IF(OR(J25=0,M25=0),0,IF(N25=3,J25*1000/(SQRT(3)*M25*O25),J25*1000/(M25*O25)))</f>
-        <v>10.1449275362319</v>
+        <v>1.0230179028133</v>
       </c>
       <c r="Q25" s="4" t="n">
         <f aca="false">IF(P25=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P25*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="R25" s="4" t="str">
         <f aca="false">IF(P25=0,"-",IF(N25=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P25*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
         <v>3x2,5 mm²</v>
       </c>
       <c r="S25" s="5" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="T25" s="5" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="U25" s="5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="n">
         <v>22</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="F26" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>125</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>28</v>
@@ -3522,18 +3555,18 @@
         <v>1</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>2.1</v>
+        <v>0.02</v>
       </c>
       <c r="K26" s="8" t="n">
         <f aca="false">H26*J26</f>
-        <v>2.1</v>
+        <v>0.02</v>
       </c>
       <c r="L26" s="8" t="n">
         <f aca="false">I26*J26</f>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="M26" s="6" t="n">
         <v>230</v>
@@ -3546,18 +3579,18 @@
       </c>
       <c r="P26" s="8" t="n">
         <f aca="false">IF(OR(J26=0,M26=0),0,IF(N26=3,J26*1000/(SQRT(3)*M26*O26),J26*1000/(M26*O26)))</f>
-        <v>10.1449275362319</v>
+        <v>0.0966183574879227</v>
       </c>
       <c r="Q26" s="4" t="n">
         <f aca="false">IF(P26=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P26*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="R26" s="4" t="str">
         <f aca="false">IF(P26=0,"-",IF(N26=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P26*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
         <v>3x2,5 mm²</v>
       </c>
       <c r="S26" s="5" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="T26" s="5" t="s">
         <v>30</v>
@@ -3566,7 +3599,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
@@ -3574,7 +3607,7 @@
         <v>132</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>133</v>
@@ -3595,15 +3628,15 @@
         <v>1</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>0.04</v>
+        <v>2.1</v>
       </c>
       <c r="K27" s="8" t="n">
         <f aca="false">H27*J27</f>
-        <v>0.04</v>
+        <v>2.1</v>
       </c>
       <c r="L27" s="8" t="n">
         <f aca="false">I27*J27</f>
-        <v>0.04</v>
+        <v>2.1</v>
       </c>
       <c r="M27" s="6" t="n">
         <v>230</v>
@@ -3616,44 +3649,44 @@
       </c>
       <c r="P27" s="8" t="n">
         <f aca="false">IF(OR(J27=0,M27=0),0,IF(N27=3,J27*1000/(SQRT(3)*M27*O27),J27*1000/(M27*O27)))</f>
-        <v>0.193236714975845</v>
+        <v>10.1449275362319</v>
       </c>
       <c r="Q27" s="4" t="n">
         <f aca="false">IF(P27=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P27*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R27" s="4" t="str">
         <f aca="false">IF(P27=0,"-",IF(N27=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P27*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
         <v>3x2,5 mm²</v>
       </c>
       <c r="S27" s="5" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="T27" s="5" t="s">
         <v>30</v>
       </c>
       <c r="U27" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="n">
         <v>24</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>28</v>
@@ -3662,18 +3695,18 @@
         <v>1</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>0.04</v>
+        <v>2.1</v>
       </c>
       <c r="K28" s="8" t="n">
         <f aca="false">H28*J28</f>
-        <v>0.04</v>
+        <v>2.1</v>
       </c>
       <c r="L28" s="8" t="n">
         <f aca="false">I28*J28</f>
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="M28" s="6" t="n">
         <v>230</v>
@@ -3686,35 +3719,35 @@
       </c>
       <c r="P28" s="8" t="n">
         <f aca="false">IF(OR(J28=0,M28=0),0,IF(N28=3,J28*1000/(SQRT(3)*M28*O28),J28*1000/(M28*O28)))</f>
-        <v>0.193236714975845</v>
+        <v>10.1449275362319</v>
       </c>
       <c r="Q28" s="4" t="n">
         <f aca="false">IF(P28=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P28*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R28" s="4" t="str">
         <f aca="false">IF(P28=0,"-",IF(N28=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P28*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
         <v>3x2,5 mm²</v>
       </c>
       <c r="S28" s="5" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="T28" s="5" t="s">
         <v>30</v>
       </c>
       <c r="U28" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="n">
         <v>25</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>143</v>
@@ -3734,67 +3767,66 @@
       <c r="I29" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="9" t="n">
-        <f aca="false">'VRF Dış Üniteler'!E5</f>
-        <v>13.8</v>
+      <c r="J29" s="7" t="n">
+        <v>0.04</v>
       </c>
       <c r="K29" s="8" t="n">
         <f aca="false">H29*J29</f>
-        <v>13.8</v>
+        <v>0.04</v>
       </c>
       <c r="L29" s="8" t="n">
         <f aca="false">I29*J29</f>
-        <v>13.8</v>
+        <v>0.04</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>400</v>
+        <v>230</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="P29" s="8" t="n">
         <f aca="false">IF(OR(J29=0,M29=0),0,IF(N29=3,J29*1000/(SQRT(3)*M29*O29),J29*1000/(M29*O29)))</f>
-        <v>20.9669308284654</v>
+        <v>0.193236714975845</v>
       </c>
       <c r="Q29" s="4" t="n">
         <f aca="false">IF(P29=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P29*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="R29" s="4" t="str">
         <f aca="false">IF(P29=0,"-",IF(N29=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P29*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
-        <v>5x6 mm²</v>
+        <v>3x2,5 mm²</v>
       </c>
       <c r="S29" s="5" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="T29" s="5" t="s">
         <v>30</v>
       </c>
       <c r="U29" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="n">
         <v>26</v>
       </c>
       <c r="B30" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>143</v>
-      </c>
       <c r="E30" s="5" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>28</v>
@@ -3805,47 +3837,46 @@
       <c r="I30" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="9" t="n">
-        <f aca="false">'VRF Dış Üniteler'!E6</f>
-        <v>13.8</v>
+      <c r="J30" s="7" t="n">
+        <v>0.04</v>
       </c>
       <c r="K30" s="8" t="n">
         <f aca="false">H30*J30</f>
-        <v>13.8</v>
+        <v>0.04</v>
       </c>
       <c r="L30" s="8" t="n">
         <f aca="false">I30*J30</f>
-        <v>13.8</v>
+        <v>0.04</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>400</v>
+        <v>230</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="P30" s="8" t="n">
         <f aca="false">IF(OR(J30=0,M30=0),0,IF(N30=3,J30*1000/(SQRT(3)*M30*O30),J30*1000/(M30*O30)))</f>
-        <v>20.9669308284654</v>
+        <v>0.193236714975845</v>
       </c>
       <c r="Q30" s="4" t="n">
         <f aca="false">IF(P30=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P30*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="R30" s="4" t="str">
         <f aca="false">IF(P30=0,"-",IF(N30=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P30*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
-        <v>5x6 mm²</v>
+        <v>3x2,5 mm²</v>
       </c>
       <c r="S30" s="5" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="T30" s="5" t="s">
         <v>30</v>
       </c>
       <c r="U30" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3853,19 +3884,19 @@
         <v>27</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>28</v>
@@ -3877,16 +3908,16 @@
         <v>1</v>
       </c>
       <c r="J31" s="9" t="n">
-        <f aca="false">'VRF Dış Üniteler'!E7</f>
-        <v>21</v>
+        <f aca="false">'VRF Dış Üniteler'!E5</f>
+        <v>13.8</v>
       </c>
       <c r="K31" s="8" t="n">
         <f aca="false">H31*J31</f>
-        <v>21</v>
+        <v>13.8</v>
       </c>
       <c r="L31" s="8" t="n">
         <f aca="false">I31*J31</f>
-        <v>21</v>
+        <v>13.8</v>
       </c>
       <c r="M31" s="6" t="n">
         <v>400</v>
@@ -3899,24 +3930,24 @@
       </c>
       <c r="P31" s="8" t="n">
         <f aca="false">IF(OR(J31=0,M31=0),0,IF(N31=3,J31*1000/(SQRT(3)*M31*O31),J31*1000/(M31*O31)))</f>
-        <v>31.9061990867951</v>
+        <v>20.9669308284654</v>
       </c>
       <c r="Q31" s="4" t="n">
         <f aca="false">IF(P31=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P31*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="R31" s="4" t="str">
         <f aca="false">IF(P31=0,"-",IF(N31=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P31*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
-        <v>5x10 mm²</v>
+        <v>5x6 mm²</v>
       </c>
       <c r="S31" s="5" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="T31" s="5" t="s">
         <v>30</v>
       </c>
       <c r="U31" s="5" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3924,10 +3955,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>152</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>142</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>153</v>
@@ -3941,55 +3972,53 @@
       <c r="G32" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H32" s="10" t="n">
-        <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G32,'VRF İç Üniteler'!$G$5:$G$34,B32,'VRF İç Üniteler'!$O$5:$O$34,"VRF-1")</f>
-        <v>3</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <f aca="false">H32</f>
-        <v>3</v>
+      <c r="H32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="J32" s="9" t="n">
-        <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B32,Tablolar!$A$5:$A$10,0))/1000</f>
-        <v>0.05</v>
+        <f aca="false">'VRF Dış Üniteler'!E6</f>
+        <v>13.8</v>
       </c>
       <c r="K32" s="8" t="n">
         <f aca="false">H32*J32</f>
-        <v>0.15</v>
+        <v>13.8</v>
       </c>
       <c r="L32" s="8" t="n">
         <f aca="false">I32*J32</f>
-        <v>0.15</v>
+        <v>13.8</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>230</v>
+        <v>400</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O32" s="7" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="P32" s="8" t="n">
         <f aca="false">IF(OR(J32=0,M32=0),0,IF(N32=3,J32*1000/(SQRT(3)*M32*O32),J32*1000/(M32*O32)))</f>
-        <v>0.241545893719807</v>
+        <v>20.9669308284654</v>
       </c>
       <c r="Q32" s="4" t="n">
         <f aca="false">IF(P32=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P32*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="R32" s="4" t="str">
         <f aca="false">IF(P32=0,"-",IF(N32=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P32*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
-        <v>3x2,5 mm²</v>
+        <v>5x6 mm²</v>
       </c>
       <c r="S32" s="5" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="T32" s="5" t="s">
         <v>30</v>
       </c>
       <c r="U32" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3997,16 +4026,16 @@
         <v>29</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>155</v>
@@ -4014,55 +4043,53 @@
       <c r="G33" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H33" s="10" t="n">
-        <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G33,'VRF İç Üniteler'!$G$5:$G$34,B33,'VRF İç Üniteler'!$O$5:$O$34,"VRF-1")</f>
-        <v>2</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <f aca="false">H33</f>
-        <v>2</v>
+      <c r="H33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="J33" s="9" t="n">
-        <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B33,Tablolar!$A$5:$A$10,0))/1000</f>
-        <v>0.062</v>
+        <f aca="false">'VRF Dış Üniteler'!E7</f>
+        <v>21</v>
       </c>
       <c r="K33" s="8" t="n">
         <f aca="false">H33*J33</f>
-        <v>0.124</v>
+        <v>21</v>
       </c>
       <c r="L33" s="8" t="n">
         <f aca="false">I33*J33</f>
-        <v>0.124</v>
+        <v>21</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>230</v>
+        <v>400</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O33" s="7" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="P33" s="8" t="n">
         <f aca="false">IF(OR(J33=0,M33=0),0,IF(N33=3,J33*1000/(SQRT(3)*M33*O33),J33*1000/(M33*O33)))</f>
-        <v>0.29951690821256</v>
+        <v>31.9061990867951</v>
       </c>
       <c r="Q33" s="4" t="n">
         <f aca="false">IF(P33=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P33*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="R33" s="4" t="str">
         <f aca="false">IF(P33=0,"-",IF(N33=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P33*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
-        <v>3x2,5 mm²</v>
+        <v>5x10 mm²</v>
       </c>
       <c r="S33" s="5" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="T33" s="5" t="s">
         <v>30</v>
       </c>
       <c r="U33" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4070,30 +4097,30 @@
         <v>30</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H34" s="10" t="n">
         <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G34,'VRF İç Üniteler'!$G$5:$G$34,B34,'VRF İç Üniteler'!$O$5:$O$34,"VRF-1")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I34" s="4" t="n">
         <f aca="false">H34</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J34" s="9" t="n">
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B34,Tablolar!$A$5:$A$10,0))/1000</f>
@@ -4101,11 +4128,11 @@
       </c>
       <c r="K34" s="8" t="n">
         <f aca="false">H34*J34</f>
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="L34" s="8" t="n">
         <f aca="false">I34*J34</f>
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="M34" s="6" t="n">
         <v>230</v>
@@ -4129,13 +4156,13 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S34" s="5" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="T34" s="5" t="s">
         <v>30</v>
       </c>
       <c r="U34" s="5" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4143,42 +4170,42 @@
         <v>31</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H35" s="10" t="n">
         <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G35,'VRF İç Üniteler'!$G$5:$G$34,B35,'VRF İç Üniteler'!$O$5:$O$34,"VRF-1")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35" s="4" t="n">
         <f aca="false">H35</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" s="9" t="n">
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B35,Tablolar!$A$5:$A$10,0))/1000</f>
-        <v>0.06</v>
+        <v>0.062</v>
       </c>
       <c r="K35" s="8" t="n">
         <f aca="false">H35*J35</f>
-        <v>0.06</v>
+        <v>0.124</v>
       </c>
       <c r="L35" s="8" t="n">
         <f aca="false">I35*J35</f>
-        <v>0.06</v>
+        <v>0.124</v>
       </c>
       <c r="M35" s="6" t="n">
         <v>230</v>
@@ -4191,7 +4218,7 @@
       </c>
       <c r="P35" s="8" t="n">
         <f aca="false">IF(OR(J35=0,M35=0),0,IF(N35=3,J35*1000/(SQRT(3)*M35*O35),J35*1000/(M35*O35)))</f>
-        <v>0.289855072463768</v>
+        <v>0.29951690821256</v>
       </c>
       <c r="Q35" s="4" t="n">
         <f aca="false">IF(P35=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P35*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
@@ -4202,13 +4229,13 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S35" s="5" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="T35" s="5" t="s">
         <v>30</v>
       </c>
       <c r="U35" s="5" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4216,30 +4243,30 @@
         <v>32</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="H36" s="10" t="n">
         <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G36,'VRF İç Üniteler'!$G$5:$G$34,B36,'VRF İç Üniteler'!$O$5:$O$34,"VRF-1")</f>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I36" s="4" t="n">
         <f aca="false">H36</f>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J36" s="9" t="n">
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B36,Tablolar!$A$5:$A$10,0))/1000</f>
@@ -4247,11 +4274,11 @@
       </c>
       <c r="K36" s="8" t="n">
         <f aca="false">H36*J36</f>
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="L36" s="8" t="n">
         <f aca="false">I36*J36</f>
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="M36" s="6" t="n">
         <v>230</v>
@@ -4275,13 +4302,13 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S36" s="5" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="T36" s="5" t="s">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="U36" s="5" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4289,30 +4316,30 @@
         <v>33</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E37" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="F37" s="5" t="s">
-        <v>163</v>
-      </c>
       <c r="G37" s="5" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="H37" s="10" t="n">
         <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G37,'VRF İç Üniteler'!$G$5:$G$34,B37,'VRF İç Üniteler'!$O$5:$O$34,"VRF-1")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" s="4" t="n">
         <f aca="false">H37</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" s="9" t="n">
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B37,Tablolar!$A$5:$A$10,0))/1000</f>
@@ -4320,11 +4347,11 @@
       </c>
       <c r="K37" s="8" t="n">
         <f aca="false">H37*J37</f>
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="L37" s="8" t="n">
         <f aca="false">I37*J37</f>
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="M37" s="6" t="n">
         <v>230</v>
@@ -4348,13 +4375,13 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S37" s="5" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="T37" s="5" t="s">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="U37" s="5" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4362,42 +4389,42 @@
         <v>34</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H38" s="10" t="n">
         <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G38,'VRF İç Üniteler'!$G$5:$G$34,B38,'VRF İç Üniteler'!$O$5:$O$34,"VRF-1")</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I38" s="4" t="n">
         <f aca="false">H38</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J38" s="9" t="n">
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B38,Tablolar!$A$5:$A$10,0))/1000</f>
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="K38" s="8" t="n">
         <f aca="false">H38*J38</f>
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="L38" s="8" t="n">
         <f aca="false">I38*J38</f>
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="M38" s="6" t="n">
         <v>230</v>
@@ -4410,7 +4437,7 @@
       </c>
       <c r="P38" s="8" t="n">
         <f aca="false">IF(OR(J38=0,M38=0),0,IF(N38=3,J38*1000/(SQRT(3)*M38*O38),J38*1000/(M38*O38)))</f>
-        <v>0.289855072463768</v>
+        <v>0.241545893719807</v>
       </c>
       <c r="Q38" s="4" t="n">
         <f aca="false">IF(P38=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P38*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
@@ -4421,13 +4448,13 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S38" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="T38" s="5" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="U38" s="5" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4435,42 +4462,42 @@
         <v>35</v>
       </c>
       <c r="B39" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>142</v>
-      </c>
       <c r="D39" s="5" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H39" s="10" t="n">
         <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G39,'VRF İç Üniteler'!$G$5:$G$34,B39,'VRF İç Üniteler'!$O$5:$O$34,"VRF-1")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" s="4" t="n">
         <f aca="false">H39</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" s="9" t="n">
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B39,Tablolar!$A$5:$A$10,0))/1000</f>
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="K39" s="8" t="n">
         <f aca="false">H39*J39</f>
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="L39" s="8" t="n">
         <f aca="false">I39*J39</f>
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="M39" s="6" t="n">
         <v>230</v>
@@ -4483,7 +4510,7 @@
       </c>
       <c r="P39" s="8" t="n">
         <f aca="false">IF(OR(J39=0,M39=0),0,IF(N39=3,J39*1000/(SQRT(3)*M39*O39),J39*1000/(M39*O39)))</f>
-        <v>0.241545893719807</v>
+        <v>0.289855072463768</v>
       </c>
       <c r="Q39" s="4" t="n">
         <f aca="false">IF(P39=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P39*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
@@ -4494,13 +4521,13 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S39" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="T39" s="5" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="U39" s="5" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4508,30 +4535,30 @@
         <v>36</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="H40" s="10" t="n">
-        <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G40,'VRF İç Üniteler'!$G$5:$G$34,B40,'VRF İç Üniteler'!$O$5:$O$34,"VRF-2")</f>
-        <v>9</v>
+        <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G40,'VRF İç Üniteler'!$G$5:$G$34,B40,'VRF İç Üniteler'!$O$5:$O$34,"VRF-1")</f>
+        <v>4</v>
       </c>
       <c r="I40" s="4" t="n">
         <f aca="false">H40</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J40" s="9" t="n">
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B40,Tablolar!$A$5:$A$10,0))/1000</f>
@@ -4539,11 +4566,11 @@
       </c>
       <c r="K40" s="8" t="n">
         <f aca="false">H40*J40</f>
-        <v>0.54</v>
+        <v>0.24</v>
       </c>
       <c r="L40" s="8" t="n">
         <f aca="false">I40*J40</f>
-        <v>0.54</v>
+        <v>0.24</v>
       </c>
       <c r="M40" s="6" t="n">
         <v>230</v>
@@ -4567,13 +4594,13 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S40" s="5" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="T40" s="5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="U40" s="5" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4581,42 +4608,42 @@
         <v>37</v>
       </c>
       <c r="B41" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E41" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>165</v>
-      </c>
       <c r="F41" s="5" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="H41" s="10" t="n">
-        <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G41,'VRF İç Üniteler'!$G$5:$G$34,B41,'VRF İç Üniteler'!$O$5:$O$34,"VRF-2")</f>
-        <v>4</v>
+        <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G41,'VRF İç Üniteler'!$G$5:$G$34,B41,'VRF İç Üniteler'!$O$5:$O$34,"VRF-1")</f>
+        <v>1</v>
       </c>
       <c r="I41" s="4" t="n">
         <f aca="false">H41</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J41" s="9" t="n">
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B41,Tablolar!$A$5:$A$10,0))/1000</f>
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="K41" s="8" t="n">
         <f aca="false">H41*J41</f>
-        <v>0.24</v>
+        <v>0.05</v>
       </c>
       <c r="L41" s="8" t="n">
         <f aca="false">I41*J41</f>
-        <v>0.24</v>
+        <v>0.05</v>
       </c>
       <c r="M41" s="6" t="n">
         <v>230</v>
@@ -4629,7 +4656,7 @@
       </c>
       <c r="P41" s="8" t="n">
         <f aca="false">IF(OR(J41=0,M41=0),0,IF(N41=3,J41*1000/(SQRT(3)*M41*O41),J41*1000/(M41*O41)))</f>
-        <v>0.289855072463768</v>
+        <v>0.241545893719807</v>
       </c>
       <c r="Q41" s="4" t="n">
         <f aca="false">IF(P41=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P41*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
@@ -4640,13 +4667,13 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S41" s="5" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="T41" s="5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="U41" s="5" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4654,42 +4681,42 @@
         <v>38</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H42" s="10" t="n">
         <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G42,'VRF İç Üniteler'!$G$5:$G$34,B42,'VRF İç Üniteler'!$O$5:$O$34,"VRF-2")</f>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I42" s="4" t="n">
         <f aca="false">H42</f>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J42" s="9" t="n">
         <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B42,Tablolar!$A$5:$A$10,0))/1000</f>
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="K42" s="8" t="n">
         <f aca="false">H42*J42</f>
-        <v>0.1</v>
+        <v>0.54</v>
       </c>
       <c r="L42" s="8" t="n">
         <f aca="false">I42*J42</f>
-        <v>0.1</v>
+        <v>0.54</v>
       </c>
       <c r="M42" s="6" t="n">
         <v>230</v>
@@ -4702,7 +4729,7 @@
       </c>
       <c r="P42" s="8" t="n">
         <f aca="false">IF(OR(J42=0,M42=0),0,IF(N42=3,J42*1000/(SQRT(3)*M42*O42),J42*1000/(M42*O42)))</f>
-        <v>0.241545893719807</v>
+        <v>0.289855072463768</v>
       </c>
       <c r="Q42" s="4" t="n">
         <f aca="false">IF(P42=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P42*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
@@ -4713,131 +4740,209 @@
         <v>3x2,5 mm²</v>
       </c>
       <c r="S42" s="5" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="T42" s="5" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="U42" s="5" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="11"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="11"/>
-      <c r="O44" s="11"/>
-      <c r="P44" s="11"/>
-      <c r="Q44" s="11"/>
-      <c r="R44" s="11"/>
-      <c r="S44" s="11"/>
-      <c r="T44" s="11"/>
-      <c r="U44" s="11"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4" t="n">
-        <f aca="false">SUMIF($C$5:$C$42,C45,$H$5:$H$42)</f>
-        <v>8</v>
-      </c>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$42,C45,$K$5:$K$42)</f>
-        <v>1.37</v>
-      </c>
-      <c r="L45" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$42,C45,$L$5:$L$42)</f>
-        <v>1.02</v>
-      </c>
-      <c r="M45" s="4"/>
-      <c r="N45" s="4"/>
-      <c r="O45" s="4"/>
-      <c r="P45" s="4"/>
-      <c r="Q45" s="4"/>
-      <c r="R45" s="4"/>
-      <c r="S45" s="4"/>
-      <c r="T45" s="4"/>
-      <c r="U45" s="4"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4" t="n">
-        <f aca="false">SUMIF($C$5:$C$42,C46,$H$5:$H$42)</f>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="H43" s="10" t="n">
+        <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G43,'VRF İç Üniteler'!$G$5:$G$34,B43,'VRF İç Üniteler'!$O$5:$O$34,"VRF-2")</f>
         <v>4</v>
       </c>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$42,C46,$K$5:$K$42)</f>
-        <v>1.55</v>
-      </c>
-      <c r="L46" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$42,C46,$L$5:$L$42)</f>
-        <v>1.55</v>
-      </c>
-      <c r="M46" s="4"/>
-      <c r="N46" s="4"/>
-      <c r="O46" s="4"/>
-      <c r="P46" s="4"/>
-      <c r="Q46" s="4"/>
-      <c r="R46" s="4"/>
-      <c r="S46" s="4"/>
-      <c r="T46" s="4"/>
-      <c r="U46" s="4"/>
+      <c r="I43" s="4" t="n">
+        <f aca="false">H43</f>
+        <v>4</v>
+      </c>
+      <c r="J43" s="9" t="n">
+        <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B43,Tablolar!$A$5:$A$10,0))/1000</f>
+        <v>0.06</v>
+      </c>
+      <c r="K43" s="8" t="n">
+        <f aca="false">H43*J43</f>
+        <v>0.24</v>
+      </c>
+      <c r="L43" s="8" t="n">
+        <f aca="false">I43*J43</f>
+        <v>0.24</v>
+      </c>
+      <c r="M43" s="6" t="n">
+        <v>230</v>
+      </c>
+      <c r="N43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" s="7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P43" s="8" t="n">
+        <f aca="false">IF(OR(J43=0,M43=0),0,IF(N43=3,J43*1000/(SQRT(3)*M43*O43),J43*1000/(M43*O43)))</f>
+        <v>0.289855072463768</v>
+      </c>
+      <c r="Q43" s="4" t="n">
+        <f aca="false">IF(P43=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P43*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
+        <v>10</v>
+      </c>
+      <c r="R43" s="4" t="str">
+        <f aca="false">IF(P43=0,"-",IF(N43=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P43*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
+        <v>3x2,5 mm²</v>
+      </c>
+      <c r="S43" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="T43" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="U43" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="H44" s="10" t="n">
+        <f aca="false">SUMIFS('VRF İç Üniteler'!$H$5:$H$34,'VRF İç Üniteler'!$A$5:$A$34,G44,'VRF İç Üniteler'!$G$5:$G$34,B44,'VRF İç Üniteler'!$O$5:$O$34,"VRF-2")</f>
+        <v>2</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <f aca="false">H44</f>
+        <v>2</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <f aca="false">INDEX(Tablolar!$E$5:$E$10,MATCH(B44,Tablolar!$A$5:$A$10,0))/1000</f>
+        <v>0.05</v>
+      </c>
+      <c r="K44" s="8" t="n">
+        <f aca="false">H44*J44</f>
+        <v>0.1</v>
+      </c>
+      <c r="L44" s="8" t="n">
+        <f aca="false">I44*J44</f>
+        <v>0.1</v>
+      </c>
+      <c r="M44" s="6" t="n">
+        <v>230</v>
+      </c>
+      <c r="N44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" s="7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P44" s="8" t="n">
+        <f aca="false">IF(OR(J44=0,M44=0),0,IF(N44=3,J44*1000/(SQRT(3)*M44*O44),J44*1000/(M44*O44)))</f>
+        <v>0.241545893719807</v>
+      </c>
+      <c r="Q44" s="4" t="n">
+        <f aca="false">IF(P44=0,"-",INDEX(Tablolar!$I$6:$I$14,MATCH(P44*1.25-0.001,Tablolar!$H$6:$H$14,1)))</f>
+        <v>10</v>
+      </c>
+      <c r="R44" s="4" t="str">
+        <f aca="false">IF(P44=0,"-",IF(N44=3,"5x","3x")&amp;INDEX(Tablolar!$J$6:$J$14,MATCH(P44*1.25-0.001,Tablolar!$H$6:$H$14,1))&amp;" mm²")</f>
+        <v>3x2,5 mm²</v>
+      </c>
+      <c r="S44" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="T44" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="U44" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="11"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="11"/>
+      <c r="P46" s="11"/>
+      <c r="Q46" s="11"/>
+      <c r="R46" s="11"/>
+      <c r="S46" s="11"/>
+      <c r="T46" s="11"/>
+      <c r="U46" s="11"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="5" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4" t="n">
-        <f aca="false">SUMIF($C$5:$C$42,C47,$H$5:$H$42)</f>
-        <v>3</v>
+        <f aca="false">SUMIF($C$5:$C$44,C47,$H$5:$H$44)</f>
+        <v>8</v>
       </c>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
       <c r="K47" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$42,C47,$K$5:$K$42)</f>
-        <v>2.6</v>
+        <f aca="false">SUMIF($C$5:$C$44,C47,$K$5:$K$44)</f>
+        <v>1.37</v>
       </c>
       <c r="L47" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$42,C47,$L$5:$L$42)</f>
-        <v>1.85</v>
+        <f aca="false">SUMIF($C$5:$C$44,C47,$L$5:$L$44)</f>
+        <v>1.02</v>
       </c>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
@@ -4853,25 +4958,25 @@
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="5" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4" t="n">
-        <f aca="false">SUMIF($C$5:$C$42,C48,$H$5:$H$42)</f>
-        <v>8</v>
+        <f aca="false">SUMIF($C$5:$C$44,C48,$H$5:$H$44)</f>
+        <v>4</v>
       </c>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
       <c r="K48" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$42,C48,$K$5:$K$42)</f>
-        <v>1.7</v>
+        <f aca="false">SUMIF($C$5:$C$44,C48,$K$5:$K$44)</f>
+        <v>1.55</v>
       </c>
       <c r="L48" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$42,C48,$L$5:$L$42)</f>
-        <v>1.7</v>
+        <f aca="false">SUMIF($C$5:$C$44,C48,$L$5:$L$44)</f>
+        <v>1.55</v>
       </c>
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
@@ -4887,25 +4992,25 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="5" t="s">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4" t="n">
-        <f aca="false">SUMIF($C$5:$C$42,C49,$H$5:$H$42)</f>
-        <v>5</v>
+        <f aca="false">SUMIF($C$5:$C$44,C49,$H$5:$H$44)</f>
+        <v>3</v>
       </c>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
       <c r="K49" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$42,C49,$K$5:$K$42)</f>
-        <v>4.3</v>
+        <f aca="false">SUMIF($C$5:$C$44,C49,$K$5:$K$44)</f>
+        <v>2.6</v>
       </c>
       <c r="L49" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$42,C49,$L$5:$L$42)</f>
-        <v>2.2</v>
+        <f aca="false">SUMIF($C$5:$C$44,C49,$L$5:$L$44)</f>
+        <v>1.85</v>
       </c>
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
@@ -4921,25 +5026,25 @@
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="5" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4" t="n">
-        <f aca="false">SUMIF($C$5:$C$42,C50,$H$5:$H$42)</f>
-        <v>40</v>
+        <f aca="false">SUMIF($C$5:$C$44,C50,$H$5:$H$44)</f>
+        <v>2</v>
       </c>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
       <c r="K50" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$42,C50,$K$5:$K$42)</f>
-        <v>50.674</v>
+        <f aca="false">SUMIF($C$5:$C$44,C50,$K$5:$K$44)</f>
+        <v>24.2</v>
       </c>
       <c r="L50" s="8" t="n">
-        <f aca="false">SUMIF($C$5:$C$42,C50,$L$5:$L$42)</f>
-        <v>50.674</v>
+        <f aca="false">SUMIF($C$5:$C$44,C50,$L$5:$L$44)</f>
+        <v>24.2</v>
       </c>
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
@@ -4951,72 +5056,174 @@
       <c r="T50" s="4"/>
       <c r="U50" s="4"/>
     </row>
-    <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="13"/>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13" t="n">
-        <f aca="false">SUM(H45:H50)</f>
-        <v>68</v>
-      </c>
-      <c r="I51" s="13"/>
-      <c r="J51" s="13"/>
-      <c r="K51" s="15" t="n">
-        <f aca="false">SUM(K45:K50)</f>
-        <v>62.194</v>
-      </c>
-      <c r="L51" s="15" t="n">
-        <f aca="false">SUM(L45:L50)</f>
-        <v>58.994</v>
-      </c>
-      <c r="M51" s="13"/>
-      <c r="N51" s="13"/>
-      <c r="O51" s="13"/>
-      <c r="P51" s="13"/>
-      <c r="Q51" s="13"/>
-      <c r="R51" s="13"/>
-      <c r="S51" s="13"/>
-      <c r="T51" s="13"/>
-      <c r="U51" s="13"/>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4" t="n">
+        <f aca="false">SUMIF($C$5:$C$44,C51,$H$5:$H$44)</f>
+        <v>8</v>
+      </c>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="8" t="n">
+        <f aca="false">SUMIF($C$5:$C$44,C51,$K$5:$K$44)</f>
+        <v>1.7</v>
+      </c>
+      <c r="L51" s="8" t="n">
+        <f aca="false">SUMIF($C$5:$C$44,C51,$L$5:$L$44)</f>
+        <v>1.7</v>
+      </c>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="4"/>
+      <c r="P51" s="4"/>
+      <c r="Q51" s="4"/>
+      <c r="R51" s="4"/>
+      <c r="S51" s="4"/>
+      <c r="T51" s="4"/>
+      <c r="U51" s="4"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4" t="n">
+        <f aca="false">SUMIF($C$5:$C$44,C52,$H$5:$H$44)</f>
+        <v>5</v>
+      </c>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="8" t="n">
+        <f aca="false">SUMIF($C$5:$C$44,C52,$K$5:$K$44)</f>
+        <v>4.3</v>
+      </c>
+      <c r="L52" s="8" t="n">
+        <f aca="false">SUMIF($C$5:$C$44,C52,$L$5:$L$44)</f>
+        <v>2.2</v>
+      </c>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
+      <c r="O52" s="4"/>
+      <c r="P52" s="4"/>
+      <c r="Q52" s="4"/>
+      <c r="R52" s="4"/>
+      <c r="S52" s="4"/>
+      <c r="T52" s="4"/>
+      <c r="U52" s="4"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="16" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="16" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="16" t="s">
-        <v>172</v>
-      </c>
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4" t="n">
+        <f aca="false">SUMIF($C$5:$C$44,C53,$H$5:$H$44)</f>
+        <v>40</v>
+      </c>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="8" t="n">
+        <f aca="false">SUMIF($C$5:$C$44,C53,$K$5:$K$44)</f>
+        <v>50.674</v>
+      </c>
+      <c r="L53" s="8" t="n">
+        <f aca="false">SUMIF($C$5:$C$44,C53,$L$5:$L$44)</f>
+        <v>50.674</v>
+      </c>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="4"/>
+      <c r="R53" s="4"/>
+      <c r="S53" s="4"/>
+      <c r="T53" s="4"/>
+      <c r="U53" s="4"/>
+    </row>
+    <row r="54" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="13"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13" t="n">
+        <f aca="false">SUM(H47:H53)</f>
+        <v>70</v>
+      </c>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="K54" s="15" t="n">
+        <f aca="false">SUM(K47:K53)</f>
+        <v>86.394</v>
+      </c>
+      <c r="L54" s="15" t="n">
+        <f aca="false">SUM(L47:L53)</f>
+        <v>83.194</v>
+      </c>
+      <c r="M54" s="13"/>
+      <c r="N54" s="13"/>
+      <c r="O54" s="13"/>
+      <c r="P54" s="13"/>
+      <c r="Q54" s="13"/>
+      <c r="R54" s="13"/>
+      <c r="S54" s="13"/>
+      <c r="T54" s="13"/>
+      <c r="U54" s="13"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="16" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="16" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="16" t="s">
-        <v>175</v>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="16" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="16" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="16" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:U42"/>
+  <autoFilter ref="A4:U44"/>
   <mergeCells count="2">
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="A2:U2"/>
@@ -5038,7 +5245,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
@@ -5050,7 +5257,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5060,7 +5267,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5073,10 +5280,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>12</v>
@@ -5085,295 +5292,319 @@
         <v>13</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="C5" s="4" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A5,'Elektrik Güç Tablosu'!$H$5:$H$42)</f>
-        <v>16</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$44,A5,'Elektrik Güç Tablosu'!$H$5:$H$44)</f>
+        <v>2</v>
       </c>
       <c r="D5" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A5,'Elektrik Güç Tablosu'!$K$5:$K$42)</f>
-        <v>5.92</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$44,A5,'Elektrik Güç Tablosu'!$K$5:$K$44)</f>
+        <v>24.2</v>
       </c>
       <c r="E5" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A5,'Elektrik Güç Tablosu'!$L$5:$L$42)</f>
-        <v>4.82</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$44,A5,'Elektrik Güç Tablosu'!$L$5:$L$44)</f>
+        <v>24.2</v>
       </c>
       <c r="F5" s="17" t="n">
-        <f aca="false">IF($E$11=0,0,E5/$E$11)</f>
-        <v>0.0817032240566837</v>
+        <f aca="false">IF($E$12=0,0,E5/$E$12)</f>
+        <v>0.290886361997259</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>146</v>
+        <v>29</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="C6" s="4" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A6,'Elektrik Güç Tablosu'!$H$5:$H$42)</f>
-        <v>3</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$44,A6,'Elektrik Güç Tablosu'!$H$5:$H$44)</f>
+        <v>16</v>
       </c>
       <c r="D6" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A6,'Elektrik Güç Tablosu'!$K$5:$K$42)</f>
-        <v>48.6</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$44,A6,'Elektrik Güç Tablosu'!$K$5:$K$44)</f>
+        <v>5.92</v>
       </c>
       <c r="E6" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A6,'Elektrik Güç Tablosu'!$L$5:$L$42)</f>
-        <v>48.6</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$44,A6,'Elektrik Güç Tablosu'!$L$5:$L$44)</f>
+        <v>4.82</v>
       </c>
       <c r="F6" s="17" t="n">
-        <f aca="false">IF($E$11=0,0,E6/$E$11)</f>
-        <v>0.823812591110961</v>
+        <f aca="false">IF($E$12=0,0,E6/$E$12)</f>
+        <v>0.057936870447388</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="C7" s="4" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A7,'Elektrik Güç Tablosu'!$H$5:$H$42)</f>
-        <v>12</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$44,A7,'Elektrik Güç Tablosu'!$H$5:$H$44)</f>
+        <v>3</v>
       </c>
       <c r="D7" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A7,'Elektrik Güç Tablosu'!$K$5:$K$42)</f>
-        <v>1.054</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$44,A7,'Elektrik Güç Tablosu'!$K$5:$K$44)</f>
+        <v>48.6</v>
       </c>
       <c r="E7" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A7,'Elektrik Güç Tablosu'!$L$5:$L$42)</f>
-        <v>1.054</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$44,A7,'Elektrik Güç Tablosu'!$L$5:$L$44)</f>
+        <v>48.6</v>
       </c>
       <c r="F7" s="17" t="n">
-        <f aca="false">IF($E$11=0,0,E7/$E$11)</f>
-        <v>0.0178662236837645</v>
+        <f aca="false">IF($E$12=0,0,E7/$E$12)</f>
+        <v>0.584176743515157</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="C8" s="4" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A8,'Elektrik Güç Tablosu'!$H$5:$H$42)</f>
-        <v>4</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$44,A8,'Elektrik Güç Tablosu'!$H$5:$H$44)</f>
+        <v>12</v>
       </c>
       <c r="D8" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A8,'Elektrik Güç Tablosu'!$K$5:$K$42)</f>
-        <v>4.28</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$44,A8,'Elektrik Güç Tablosu'!$K$5:$K$44)</f>
+        <v>1.054</v>
       </c>
       <c r="E8" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A8,'Elektrik Güç Tablosu'!$L$5:$L$42)</f>
-        <v>2.18</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$44,A8,'Elektrik Güç Tablosu'!$L$5:$L$44)</f>
+        <v>1.054</v>
       </c>
       <c r="F8" s="17" t="n">
-        <f aca="false">IF($E$11=0,0,E8/$E$11)</f>
-        <v>0.0369529104654711</v>
+        <f aca="false">IF($E$12=0,0,E8/$E$12)</f>
+        <v>0.0126691828737649</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="C9" s="4" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A9,'Elektrik Güç Tablosu'!$H$5:$H$42)</f>
-        <v>15</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$44,A9,'Elektrik Güç Tablosu'!$H$5:$H$44)</f>
+        <v>4</v>
       </c>
       <c r="D9" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A9,'Elektrik Güç Tablosu'!$K$5:$K$42)</f>
-        <v>1.01</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$44,A9,'Elektrik Güç Tablosu'!$K$5:$K$44)</f>
+        <v>4.28</v>
       </c>
       <c r="E9" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A9,'Elektrik Güç Tablosu'!$L$5:$L$42)</f>
-        <v>1.01</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$44,A9,'Elektrik Güç Tablosu'!$L$5:$L$44)</f>
+        <v>2.18</v>
       </c>
       <c r="F9" s="17" t="n">
-        <f aca="false">IF($E$11=0,0,E9/$E$11)</f>
-        <v>0.0171203851239109</v>
+        <f aca="false">IF($E$12=0,0,E9/$E$12)</f>
+        <v>0.0262038127749597</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="C10" s="4" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A10,'Elektrik Güç Tablosu'!$H$5:$H$42)</f>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$44,A10,'Elektrik Güç Tablosu'!$H$5:$H$44)</f>
+        <v>15</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$44,A10,'Elektrik Güç Tablosu'!$K$5:$K$44)</f>
+        <v>1.01</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$44,A10,'Elektrik Güç Tablosu'!$L$5:$L$44)</f>
+        <v>1.01</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <f aca="false">IF($E$12=0,0,E10/$E$12)</f>
+        <v>0.0121402985792245</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$44,A11,'Elektrik Güç Tablosu'!$H$5:$H$44)</f>
         <v>17</v>
       </c>
-      <c r="D10" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A10,'Elektrik Güç Tablosu'!$K$5:$K$42)</f>
+      <c r="D11" s="8" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$44,A11,'Elektrik Güç Tablosu'!$K$5:$K$44)</f>
         <v>1.33</v>
       </c>
-      <c r="E10" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$42,A10,'Elektrik Güç Tablosu'!$L$5:$L$42)</f>
+      <c r="E11" s="8" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$S$5:$S$44,A11,'Elektrik Güç Tablosu'!$L$5:$L$44)</f>
         <v>1.33</v>
       </c>
-      <c r="F10" s="17" t="n">
-        <f aca="false">IF($E$11=0,0,E10/$E$11)</f>
-        <v>0.0225446655592094</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13" t="n">
-        <f aca="false">SUM(C5:C10)</f>
-        <v>67</v>
-      </c>
-      <c r="D11" s="15" t="n">
-        <f aca="false">SUM(D5:D10)</f>
-        <v>62.194</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <f aca="false">SUM(E5:E10)</f>
-        <v>58.994</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <f aca="false">SUM(F5:F10)</f>
-        <v>1</v>
+      <c r="F11" s="17" t="n">
+        <f aca="false">IF($E$12=0,0,E11/$E$12)</f>
+        <v>0.0159867298122461</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13" t="n">
+        <f aca="false">SUM(C5:C11)</f>
+        <v>69</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <f aca="false">SUM(D5:D11)</f>
+        <v>86.394</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <f aca="false">SUM(E5:E11)</f>
+        <v>83.194</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <f aca="false">SUM(F5:F11)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <f aca="false">D12-'Elektrik Güç Tablosu'!K54</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D12" s="19" t="n">
-        <f aca="false">D11-'Elektrik Güç Tablosu'!K51</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="C15" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$42,A15,'Elektrik Güç Tablosu'!$H$5:$H$42)</f>
-        <v>36</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$42,A15,'Elektrik Güç Tablosu'!$K$5:$K$42)</f>
-        <v>59.854</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$42,A15,'Elektrik Güç Tablosu'!$L$5:$L$42)</f>
-        <v>56.654</v>
-      </c>
-      <c r="F15" s="17" t="n">
-        <f aca="false">IF($E$18=0,0,E15/$E$18)</f>
-        <v>0.96033494931688</v>
+      <c r="F15" s="3" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="C16" s="4" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$42,A16,'Elektrik Güç Tablosu'!$H$5:$H$42)</f>
-        <v>15</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$44,A16,'Elektrik Güç Tablosu'!$H$5:$H$44)</f>
+        <v>38</v>
       </c>
       <c r="D16" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$42,A16,'Elektrik Güç Tablosu'!$K$5:$K$42)</f>
-        <v>1.01</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$44,A16,'Elektrik Güç Tablosu'!$K$5:$K$44)</f>
+        <v>84.054</v>
       </c>
       <c r="E16" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$42,A16,'Elektrik Güç Tablosu'!$L$5:$L$42)</f>
-        <v>1.01</v>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$44,A16,'Elektrik Güç Tablosu'!$L$5:$L$44)</f>
+        <v>80.854</v>
       </c>
       <c r="F16" s="17" t="n">
-        <f aca="false">IF($E$18=0,0,E16/$E$18)</f>
-        <v>0.0171203851239109</v>
+        <f aca="false">IF($E$19=0,0,E16/$E$19)</f>
+        <v>0.971872971608529</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="C17" s="4" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$42,A17,'Elektrik Güç Tablosu'!$H$5:$H$42)</f>
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$44,A17,'Elektrik Güç Tablosu'!$H$5:$H$44)</f>
+        <v>15</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$44,A17,'Elektrik Güç Tablosu'!$K$5:$K$44)</f>
+        <v>1.01</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$44,A17,'Elektrik Güç Tablosu'!$L$5:$L$44)</f>
+        <v>1.01</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <f aca="false">IF($E$19=0,0,E17/$E$19)</f>
+        <v>0.0121402985792245</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$44,A18,'Elektrik Güç Tablosu'!$H$5:$H$44)</f>
         <v>17</v>
       </c>
-      <c r="D17" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$42,A17,'Elektrik Güç Tablosu'!$K$5:$K$42)</f>
+      <c r="D18" s="8" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$44,A18,'Elektrik Güç Tablosu'!$K$5:$K$44)</f>
         <v>1.33</v>
       </c>
-      <c r="E17" s="8" t="n">
-        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$42,A17,'Elektrik Güç Tablosu'!$L$5:$L$42)</f>
+      <c r="E18" s="8" t="n">
+        <f aca="false">SUMIF('Elektrik Güç Tablosu'!$G$5:$G$44,A18,'Elektrik Güç Tablosu'!$L$5:$L$44)</f>
         <v>1.33</v>
       </c>
-      <c r="F17" s="17" t="n">
-        <f aca="false">IF($E$18=0,0,E17/$E$18)</f>
-        <v>0.0225446655592094</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13" t="n">
-        <f aca="false">SUM(C15:C17)</f>
-        <v>68</v>
-      </c>
-      <c r="D18" s="15" t="n">
-        <f aca="false">SUM(D15:D17)</f>
-        <v>62.194</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <f aca="false">SUM(E15:E17)</f>
-        <v>58.994</v>
-      </c>
-      <c r="F18" s="18" t="n">
-        <f aca="false">SUM(F15:F17)</f>
+      <c r="F18" s="17" t="n">
+        <f aca="false">IF($E$19=0,0,E18/$E$19)</f>
+        <v>0.0159867298122461</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13" t="n">
+        <f aca="false">SUM(C16:C18)</f>
+        <v>70</v>
+      </c>
+      <c r="D19" s="15" t="n">
+        <f aca="false">SUM(D16:D18)</f>
+        <v>86.394</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <f aca="false">SUM(E16:E18)</f>
+        <v>83.194</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <f aca="false">SUM(F16:F18)</f>
         <v>1</v>
       </c>
     </row>
@@ -5413,7 +5644,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5425,7 +5656,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5437,33 +5668,33 @@
     </row>
     <row r="4" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>2.2</v>
@@ -5475,24 +5706,24 @@
         <v>50</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>2.8</v>
@@ -5504,7 +5735,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0</v>
@@ -5513,15 +5744,15 @@
         <v>10</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>3.6</v>
@@ -5533,7 +5764,7 @@
         <v>60</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>10</v>
@@ -5542,15 +5773,15 @@
         <v>16</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>4.5</v>
@@ -5562,7 +5793,7 @@
         <v>60</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>16</v>
@@ -5571,15 +5802,15 @@
         <v>20</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>5.6</v>
@@ -5591,7 +5822,7 @@
         <v>62</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>20</v>
@@ -5600,15 +5831,15 @@
         <v>25</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>7.1</v>
@@ -5620,7 +5851,7 @@
         <v>62</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>25</v>
@@ -5629,7 +5860,7 @@
         <v>32</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5640,7 +5871,7 @@
         <v>40</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5651,7 +5882,7 @@
         <v>50</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5662,7 +5893,7 @@
         <v>63</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5673,12 +5904,12 @@
         <v>80</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H17" s="16" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -5727,7 +5958,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5763,7 +5994,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5799,18 +6030,18 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="O4" s="20" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="21"/>
@@ -5818,45 +6049,45 @@
         <v>38.5</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="21"/>
@@ -5864,13 +6095,13 @@
         <v>24</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>37</v>
@@ -5882,7 +6113,7 @@
         <v>10</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="P6" s="6" t="n">
         <v>10</v>
@@ -5900,7 +6131,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="B7" s="21"/>
       <c r="C7" s="21"/>
@@ -5908,13 +6139,13 @@
         <v>1.8</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>217</v>
@@ -5926,7 +6157,7 @@
         <v>17</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="P7" s="6"/>
       <c r="Q7" s="6" t="n">
@@ -5944,7 +6175,7 @@
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="B8" s="21"/>
       <c r="C8" s="21"/>
@@ -5952,13 +6183,13 @@
         <v>0.55</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>307</v>
@@ -5970,7 +6201,7 @@
         <v>15</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="P8" s="6"/>
       <c r="Q8" s="6" t="n">
@@ -5988,7 +6219,7 @@
     </row>
     <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="B9" s="21"/>
       <c r="C9" s="21"/>
@@ -5996,13 +6227,13 @@
         <v>0.7</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>127</v>
@@ -6014,7 +6245,7 @@
         <v>13</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="P9" s="6" t="n">
         <v>2</v>
@@ -6032,7 +6263,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="B10" s="21"/>
       <c r="C10" s="21"/>
@@ -6040,10 +6271,10 @@
         <v>0.5</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="P10" s="6" t="n">
         <v>1.5</v>
@@ -6061,7 +6292,7 @@
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="B11" s="21"/>
       <c r="C11" s="21"/>
@@ -6069,13 +6300,13 @@
         <v>0.4</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="P11" s="6" t="n">
         <v>1.5</v>
@@ -6093,7 +6324,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
@@ -6101,10 +6332,10 @@
         <v>22</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="P12" s="6" t="n">
         <v>4</v>
@@ -6122,7 +6353,7 @@
     </row>
     <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
@@ -6130,10 +6361,10 @@
         <v>4</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="P13" s="6"/>
       <c r="Q13" s="6" t="n">
@@ -6151,7 +6382,7 @@
     </row>
     <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
@@ -6159,10 +6390,10 @@
         <v>3</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="P14" s="6" t="n">
         <v>3</v>
@@ -6180,7 +6411,7 @@
     </row>
     <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
@@ -6189,7 +6420,7 @@
       </c>
       <c r="E15" s="16"/>
       <c r="O15" s="4" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="P15" s="6"/>
       <c r="Q15" s="6" t="n">
@@ -6207,7 +6438,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="21"/>
@@ -6215,12 +6446,12 @@
         <v>10</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
@@ -6234,88 +6465,88 @@
         <v>8</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="W18" s="3" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="X18" s="3" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="Y18" s="3" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="Z18" s="3" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="AA18" s="3" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="AB18" s="3" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="AC18" s="3" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6323,13 +6554,13 @@
         <v>28</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>8.35</v>
@@ -6365,7 +6596,7 @@
         <v>0</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="Q19" s="23" t="n">
         <f aca="false">(H19*$K$6+J19*$K$7+L19*$K$8+N19*$K$9)*$D$8*$D$9</f>
@@ -6425,13 +6656,13 @@
         <v>28</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>42.5</v>
@@ -6467,7 +6698,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="5" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="Q20" s="23" t="n">
         <f aca="false">(H20*$K$6+J20*$K$7+L20*$K$8+N20*$K$9)*$D$8*$D$9</f>
@@ -6527,13 +6758,13 @@
         <v>28</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>19.7</v>
@@ -6569,7 +6800,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="5" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="Q21" s="23" t="n">
         <f aca="false">(H21*$K$6+J21*$K$7+L21*$K$8+N21*$K$9)*$D$8*$D$9</f>
@@ -6629,13 +6860,13 @@
         <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>17.66</v>
@@ -6671,7 +6902,7 @@
         <v>0</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="Q22" s="23" t="n">
         <f aca="false">(H22*$K$6+J22*$K$7+L22*$K$8+N22*$K$9)*$D$8*$D$9</f>
@@ -6731,13 +6962,13 @@
         <v>28</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>22.15</v>
@@ -6773,7 +7004,7 @@
         <v>0</v>
       </c>
       <c r="P23" s="5" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="Q23" s="23" t="n">
         <f aca="false">(H23*$K$6+J23*$K$7+L23*$K$8+N23*$K$9)*$D$8*$D$9</f>
@@ -6833,13 +7064,13 @@
         <v>28</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>16.07</v>
@@ -6875,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="5" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="Q24" s="23" t="n">
         <f aca="false">(H24*$K$6+J24*$K$7+L24*$K$8+N24*$K$9)*$D$8*$D$9</f>
@@ -6935,13 +7166,13 @@
         <v>28</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>16.4</v>
@@ -6977,7 +7208,7 @@
         <v>0</v>
       </c>
       <c r="P25" s="5" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="Q25" s="23" t="n">
         <f aca="false">(H25*$K$6+J25*$K$7+L25*$K$8+N25*$K$9)*$D$8*$D$9</f>
@@ -7034,16 +7265,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>42.65</v>
@@ -7079,7 +7310,7 @@
         <v>0</v>
       </c>
       <c r="P26" s="5" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="Q26" s="23" t="n">
         <f aca="false">(H26*$K$6+J26*$K$7+L26*$K$8+N26*$K$9)*$D$8*$D$9</f>
@@ -7136,16 +7367,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>43.8</v>
@@ -7181,7 +7412,7 @@
         <v>0</v>
       </c>
       <c r="P27" s="5" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="Q27" s="23" t="n">
         <f aca="false">(H27*$K$6+J27*$K$7+L27*$K$8+N27*$K$9)*$D$8*$D$9</f>
@@ -7238,16 +7469,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>27.5</v>
@@ -7283,7 +7514,7 @@
         <v>0</v>
       </c>
       <c r="P28" s="5" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="Q28" s="23" t="n">
         <f aca="false">(H28*$K$6+J28*$K$7+L28*$K$8+N28*$K$9)*$D$8*$D$9</f>
@@ -7340,16 +7571,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>24.15</v>
@@ -7385,7 +7616,7 @@
         <v>0</v>
       </c>
       <c r="P29" s="5" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="Q29" s="23" t="n">
         <f aca="false">(H29*$K$6+J29*$K$7+L29*$K$8+N29*$K$9)*$D$8*$D$9</f>
@@ -7442,16 +7673,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="E30" s="6" t="n">
         <v>21.8</v>
@@ -7487,7 +7718,7 @@
         <v>0</v>
       </c>
       <c r="P30" s="5" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="Q30" s="23" t="n">
         <f aca="false">(H30*$K$6+J30*$K$7+L30*$K$8+N30*$K$9)*$D$8*$D$9</f>
@@ -7544,16 +7775,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="E31" s="6" t="n">
         <v>24</v>
@@ -7589,7 +7820,7 @@
         <v>0</v>
       </c>
       <c r="P31" s="5" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="Q31" s="23" t="n">
         <f aca="false">(H31*$K$6+J31*$K$7+L31*$K$8+N31*$K$9)*$D$8*$D$9</f>
@@ -7646,16 +7877,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>19.48</v>
@@ -7691,7 +7922,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="5" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="Q32" s="23" t="n">
         <f aca="false">(H32*$K$6+J32*$K$7+L32*$K$8+N32*$K$9)*$D$8*$D$9</f>
@@ -7748,16 +7979,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>24.53</v>
@@ -7793,7 +8024,7 @@
         <v>0</v>
       </c>
       <c r="P33" s="5" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="Q33" s="23" t="n">
         <f aca="false">(H33*$K$6+J33*$K$7+L33*$K$8+N33*$K$9)*$D$8*$D$9</f>
@@ -7850,16 +8081,16 @@
     </row>
     <row r="34" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="E34" s="6" t="n">
         <v>39.9</v>
@@ -7895,7 +8126,7 @@
         <v>0</v>
       </c>
       <c r="P34" s="5" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="Q34" s="23" t="n">
         <f aca="false">(H34*$K$6+J34*$K$7+L34*$K$8+N34*$K$9)*$D$8*$D$9</f>
@@ -7952,16 +8183,16 @@
     </row>
     <row r="35" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>39.65</v>
@@ -7997,7 +8228,7 @@
         <v>0</v>
       </c>
       <c r="P35" s="5" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="Q35" s="23" t="n">
         <f aca="false">(H35*$K$6+J35*$K$7+L35*$K$8+N35*$K$9)*$D$8*$D$9</f>
@@ -8054,16 +8285,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>24</v>
@@ -8099,7 +8330,7 @@
         <v>1</v>
       </c>
       <c r="P36" s="5" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="Q36" s="23" t="n">
         <f aca="false">(H36*$K$6+J36*$K$7+L36*$K$8+N36*$K$9)*$D$8*$D$9</f>
@@ -8156,16 +8387,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>23.75</v>
@@ -8201,7 +8432,7 @@
         <v>1</v>
       </c>
       <c r="P37" s="5" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="Q37" s="23" t="n">
         <f aca="false">(H37*$K$6+J37*$K$7+L37*$K$8+N37*$K$9)*$D$8*$D$9</f>
@@ -8258,16 +8489,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>22.95</v>
@@ -8303,7 +8534,7 @@
         <v>1</v>
       </c>
       <c r="P38" s="5" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="Q38" s="23" t="n">
         <f aca="false">(H38*$K$6+J38*$K$7+L38*$K$8+N38*$K$9)*$D$8*$D$9</f>
@@ -8360,16 +8591,16 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>15.37</v>
@@ -8405,7 +8636,7 @@
         <v>1</v>
       </c>
       <c r="P39" s="5" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="Q39" s="23" t="n">
         <f aca="false">(H39*$K$6+J39*$K$7+L39*$K$8+N39*$K$9)*$D$8*$D$9</f>
@@ -8462,16 +8693,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="E40" s="6" t="n">
         <v>16.26</v>
@@ -8507,7 +8738,7 @@
         <v>1</v>
       </c>
       <c r="P40" s="5" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Q40" s="23" t="n">
         <f aca="false">(H40*$K$6+J40*$K$7+L40*$K$8+N40*$K$9)*$D$8*$D$9</f>
@@ -8564,16 +8795,16 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="E41" s="6" t="n">
         <v>21.8</v>
@@ -8609,7 +8840,7 @@
         <v>1</v>
       </c>
       <c r="P41" s="5" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="Q41" s="23" t="n">
         <f aca="false">(H41*$K$6+J41*$K$7+L41*$K$8+N41*$K$9)*$D$8*$D$9</f>
@@ -8666,16 +8897,16 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="E42" s="6" t="n">
         <v>24</v>
@@ -8711,7 +8942,7 @@
         <v>1</v>
       </c>
       <c r="P42" s="5" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="Q42" s="23" t="n">
         <f aca="false">(H42*$K$6+J42*$K$7+L42*$K$8+N42*$K$9)*$D$8*$D$9</f>
@@ -8768,16 +8999,16 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="E43" s="6" t="n">
         <v>18.48</v>
@@ -8813,7 +9044,7 @@
         <v>1</v>
       </c>
       <c r="P43" s="5" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="Q43" s="23" t="n">
         <f aca="false">(H43*$K$6+J43*$K$7+L43*$K$8+N43*$K$9)*$D$8*$D$9</f>
@@ -8870,16 +9101,16 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="E44" s="6" t="n">
         <v>24.55</v>
@@ -8915,7 +9146,7 @@
         <v>1</v>
       </c>
       <c r="P44" s="5" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="Q44" s="23" t="n">
         <f aca="false">(H44*$K$6+J44*$K$7+L44*$K$8+N44*$K$9)*$D$8*$D$9</f>
@@ -8972,16 +9203,16 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="E45" s="6" t="n">
         <v>43.05</v>
@@ -9017,7 +9248,7 @@
         <v>1</v>
       </c>
       <c r="P45" s="5" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="Q45" s="23" t="n">
         <f aca="false">(H45*$K$6+J45*$K$7+L45*$K$8+N45*$K$9)*$D$8*$D$9</f>
@@ -9074,16 +9305,16 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E46" s="6" t="n">
         <v>14.45</v>
@@ -9119,7 +9350,7 @@
         <v>1</v>
       </c>
       <c r="P46" s="5" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="Q46" s="23" t="n">
         <f aca="false">(H46*$K$6+J46*$K$7+L46*$K$8+N46*$K$9)*$D$8*$D$9</f>
@@ -9176,16 +9407,16 @@
     </row>
     <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="E47" s="6" t="n">
         <v>42.17</v>
@@ -9221,7 +9452,7 @@
         <v>1</v>
       </c>
       <c r="P47" s="5" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="Q47" s="23" t="n">
         <f aca="false">(H47*$K$6+J47*$K$7+L47*$K$8+N47*$K$9)*$D$8*$D$9</f>
@@ -9278,16 +9509,16 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="E48" s="6" t="n">
         <v>21.92</v>
@@ -9323,7 +9554,7 @@
         <v>1</v>
       </c>
       <c r="P48" s="5" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="Q48" s="23" t="n">
         <f aca="false">(H48*$K$6+J48*$K$7+L48*$K$8+N48*$K$9)*$D$8*$D$9</f>
@@ -9382,7 +9613,7 @@
       <c r="A49" s="13"/>
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="D49" s="13"/>
       <c r="E49" s="13" t="n">
@@ -9455,75 +9686,75 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="16" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="16" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="16" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="16" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="16" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="20" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="C59" s="6" t="n">
         <v>11.4</v>
@@ -9532,7 +9763,7 @@
         <v>2500</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="F59" s="4" t="n">
         <f aca="false">C59*$D$16</f>
@@ -9559,10 +9790,10 @@
     </row>
     <row r="60" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="C60" s="6" t="n">
         <v>10.62</v>
@@ -9571,7 +9802,7 @@
         <v>1000</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="F60" s="4" t="n">
         <f aca="false">C60*$D$16</f>
@@ -9599,7 +9830,7 @@
     <row r="61" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="13"/>
       <c r="B61" s="14" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="C61" s="13"/>
       <c r="D61" s="13"/>
@@ -9621,7 +9852,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="16" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -9678,7 +9909,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9698,7 +9929,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -9721,49 +9952,49 @@
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>364</v>
-      </c>
       <c r="L4" s="3" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9771,10 +10002,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>8.35</v>
@@ -9788,7 +10019,7 @@
         <v>0.67439920625</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>1</v>
@@ -9818,10 +10049,10 @@
         <v>0.05</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9829,10 +10060,10 @@
         <v>28</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>42.5</v>
@@ -9846,7 +10077,7 @@
         <v>9.5582306875</v>
       </c>
       <c r="G6" s="30" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>2</v>
@@ -9876,10 +10107,10 @@
         <v>0.124</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9887,10 +10118,10 @@
         <v>28</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>19.7</v>
@@ -9904,7 +10135,7 @@
         <v>2.5830025375</v>
       </c>
       <c r="G7" s="30" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>1</v>
@@ -9934,10 +10165,10 @@
         <v>0.05</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9945,10 +10176,10 @@
         <v>28</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>17.66</v>
@@ -9962,7 +10193,7 @@
         <v>2.0214118925</v>
       </c>
       <c r="G8" s="30" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>1</v>
@@ -9992,10 +10223,10 @@
         <v>0.05</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10003,10 +10234,10 @@
         <v>28</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>22.15</v>
@@ -10020,7 +10251,7 @@
         <v>2.24642268125</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>1</v>
@@ -10050,10 +10281,10 @@
         <v>0.05</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10061,10 +10292,10 @@
         <v>28</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>16.07</v>
@@ -10078,7 +10309,7 @@
         <v>1.91703054125</v>
       </c>
       <c r="G10" s="30" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>1</v>
@@ -10108,10 +10339,10 @@
         <v>0.05</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10119,10 +10350,10 @@
         <v>28</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>16.4</v>
@@ -10136,7 +10367,7 @@
         <v>2.92268295</v>
       </c>
       <c r="G11" s="30" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>1</v>
@@ -10166,21 +10397,21 @@
         <v>0.06</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>42.65</v>
@@ -10194,7 +10425,7 @@
         <v>4.99946981875</v>
       </c>
       <c r="G12" s="30" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>2</v>
@@ -10224,21 +10455,21 @@
         <v>0.1</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>43.8</v>
@@ -10252,7 +10483,7 @@
         <v>5.170177925</v>
       </c>
       <c r="G13" s="30" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>2</v>
@@ -10282,21 +10513,21 @@
         <v>0.1</v>
       </c>
       <c r="O13" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>27.5</v>
@@ -10310,7 +10541,7 @@
         <v>2.7385422625</v>
       </c>
       <c r="G14" s="30" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>1</v>
@@ -10340,21 +10571,21 @@
         <v>0.05</v>
       </c>
       <c r="O14" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>24.15</v>
@@ -10368,7 +10599,7 @@
         <v>4.05655903125</v>
       </c>
       <c r="G15" s="30" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>1</v>
@@ -10398,21 +10629,21 @@
         <v>0.06</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>21.8</v>
@@ -10426,7 +10657,7 @@
         <v>3.809015375</v>
       </c>
       <c r="G16" s="30" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>1</v>
@@ -10456,21 +10687,21 @@
         <v>0.06</v>
       </c>
       <c r="O16" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="P16" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>24</v>
@@ -10484,7 +10715,7 @@
         <v>3.540856</v>
       </c>
       <c r="G17" s="30" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>1</v>
@@ -10514,21 +10745,21 @@
         <v>0.06</v>
       </c>
       <c r="O17" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>19.48</v>
@@ -10542,7 +10773,7 @@
         <v>2.132879265</v>
       </c>
       <c r="G18" s="30" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>1</v>
@@ -10572,21 +10803,21 @@
         <v>0.05</v>
       </c>
       <c r="O18" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="P18" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D19" s="7" t="n">
         <v>24.53</v>
@@ -10600,7 +10831,7 @@
         <v>3.56077888375</v>
       </c>
       <c r="G19" s="30" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>1</v>
@@ -10630,21 +10861,21 @@
         <v>0.06</v>
       </c>
       <c r="O19" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>39.9</v>
@@ -10658,7 +10889,7 @@
         <v>5.3914920125</v>
       </c>
       <c r="G20" s="30" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>2</v>
@@ -10688,21 +10919,21 @@
         <v>0.1</v>
       </c>
       <c r="O20" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="P20" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>39.65</v>
@@ -10716,7 +10947,7 @@
         <v>5.64809499375</v>
       </c>
       <c r="G21" s="30" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H21" s="6" t="n">
         <v>2</v>
@@ -10746,21 +10977,21 @@
         <v>0.12</v>
       </c>
       <c r="O21" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="P21" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>24</v>
@@ -10774,7 +11005,7 @@
         <v>3.4486122</v>
       </c>
       <c r="G22" s="30" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H22" s="6" t="n">
         <v>1</v>
@@ -10804,21 +11035,21 @@
         <v>0.06</v>
       </c>
       <c r="O22" s="5" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>23.75</v>
@@ -10832,7 +11063,7 @@
         <v>3.24369148125</v>
       </c>
       <c r="G23" s="30" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>1</v>
@@ -10862,21 +11093,21 @@
         <v>0.06</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="P23" s="5" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>22.95</v>
@@ -10890,7 +11121,7 @@
         <v>3.20192558125</v>
       </c>
       <c r="G24" s="30" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>1</v>
@@ -10920,21 +11151,21 @@
         <v>0.06</v>
       </c>
       <c r="O24" s="5" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="P24" s="5" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>15.37</v>
@@ -10948,7 +11179,7 @@
         <v>3.45041142875</v>
       </c>
       <c r="G25" s="30" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H25" s="6" t="n">
         <v>1</v>
@@ -10978,21 +11209,21 @@
         <v>0.06</v>
       </c>
       <c r="O25" s="5" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="P25" s="5" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>16.26</v>
@@ -11006,7 +11237,7 @@
         <v>3.3840602675</v>
       </c>
       <c r="G26" s="30" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>1</v>
@@ -11036,21 +11267,21 @@
         <v>0.06</v>
       </c>
       <c r="O26" s="5" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="P26" s="5" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>21.8</v>
@@ -11064,7 +11295,7 @@
         <v>4.020039375</v>
       </c>
       <c r="G27" s="30" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H27" s="6" t="n">
         <v>1</v>
@@ -11094,21 +11325,21 @@
         <v>0.06</v>
       </c>
       <c r="O27" s="5" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="P27" s="5" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>24</v>
@@ -11122,7 +11353,7 @@
         <v>3.773176</v>
       </c>
       <c r="G28" s="30" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>1</v>
@@ -11152,21 +11383,21 @@
         <v>0.06</v>
       </c>
       <c r="O28" s="5" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="P28" s="5" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>18.48</v>
@@ -11180,7 +11411,7 @@
         <v>2.27625079</v>
       </c>
       <c r="G29" s="30" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H29" s="6" t="n">
         <v>1</v>
@@ -11210,21 +11441,21 @@
         <v>0.05</v>
       </c>
       <c r="O29" s="5" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="P29" s="5" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>24.55</v>
@@ -11238,7 +11469,7 @@
         <v>3.79913318125</v>
       </c>
       <c r="G30" s="30" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H30" s="6" t="n">
         <v>1</v>
@@ -11268,21 +11499,21 @@
         <v>0.06</v>
       </c>
       <c r="O30" s="5" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="P30" s="5" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="D31" s="7" t="n">
         <v>43.05</v>
@@ -11296,7 +11527,7 @@
         <v>5.66132936875</v>
       </c>
       <c r="G31" s="30" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H31" s="6" t="n">
         <v>2</v>
@@ -11326,21 +11557,21 @@
         <v>0.12</v>
       </c>
       <c r="O31" s="5" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="P31" s="5" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>14.45</v>
@@ -11354,7 +11585,7 @@
         <v>2.29899044375</v>
       </c>
       <c r="G32" s="30" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H32" s="6" t="n">
         <v>1</v>
@@ -11384,21 +11615,21 @@
         <v>0.05</v>
       </c>
       <c r="O32" s="5" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="P32" s="5" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="D33" s="7" t="n">
         <v>42.17</v>
@@ -11412,7 +11643,7 @@
         <v>6.17511637875</v>
       </c>
       <c r="G33" s="30" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H33" s="6" t="n">
         <v>2</v>
@@ -11442,21 +11673,21 @@
         <v>0.12</v>
       </c>
       <c r="O33" s="5" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="P33" s="5" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>21.92</v>
@@ -11470,7 +11701,7 @@
         <v>4.39054836</v>
       </c>
       <c r="G34" s="30" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H34" s="6" t="n">
         <v>1</v>
@@ -11500,17 +11731,17 @@
         <v>0.06</v>
       </c>
       <c r="O34" s="5" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="P34" s="5" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13"/>
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="D35" s="15" t="n">
         <f aca="false">SUM(D5:D34)</f>
@@ -11546,12 +11777,12 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="16" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -11590,7 +11821,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11605,7 +11836,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11623,42 +11854,42 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>12</v>
@@ -11670,13 +11901,13 @@
         <v>13.8</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="I5" s="8" t="n">
         <f aca="false">SUMIF('VRF İç Üniteler'!$O$5:$O$34,A5,'VRF İç Üniteler'!$J$5:$J$34)</f>
@@ -11693,10 +11924,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>12</v>
@@ -11708,13 +11939,13 @@
         <v>13.8</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="I6" s="8" t="n">
         <f aca="false">SUMIF('VRF İç Üniteler'!$O$5:$O$34,A6,'VRF İç Üniteler'!$J$5:$J$34)</f>
@@ -11731,10 +11962,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>18</v>
@@ -11746,13 +11977,13 @@
         <v>21</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="I7" s="8" t="n">
         <f aca="false">SUMIF('VRF İç Üniteler'!$O$5:$O$34,A7,'VRF İç Üniteler'!$J$5:$J$34)</f>
@@ -11770,7 +12001,7 @@
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13"/>
       <c r="B8" s="14" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="C8" s="13" t="n">
         <f aca="false">SUM(C5:C7)</f>
@@ -11793,17 +12024,17 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
